--- a/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
+++ b/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B13800-2231-4232-9677-28348639D7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ACD6E8-AECC-451D-B742-525C54790970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
   </bookViews>
   <sheets>
-    <sheet name="ゲームの仕様" sheetId="1" r:id="rId1"/>
-    <sheet name="シナリオ" sheetId="2" r:id="rId2"/>
-    <sheet name="イベント" sheetId="3" r:id="rId3"/>
-    <sheet name="フローチャート" sheetId="5" r:id="rId4"/>
+    <sheet name="コンセプト" sheetId="7" r:id="rId1"/>
+    <sheet name="マップ" sheetId="8" r:id="rId2"/>
+    <sheet name="ゲームの仕様" sheetId="1" r:id="rId3"/>
+    <sheet name="シナリオ" sheetId="2" r:id="rId4"/>
+    <sheet name="イベント" sheetId="3" r:id="rId5"/>
+    <sheet name="フローチャート" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="176">
   <si>
     <t>更新日</t>
     <rPh sb="0" eb="3">
@@ -2112,6 +2113,266 @@
     <t>フローチャート設定</t>
     <rPh sb="7" eb="9">
       <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特殊問題について</t>
+    <rPh sb="0" eb="4">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特殊問題（職員室で獲得するカギ）は間違えても見回りの先生に捕まらない（ゲームオーバーにならない）とする</t>
+    <rPh sb="0" eb="4">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ショクインシツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（特殊問題はこっちの自我で作ってるので、プレイヤーを巻き込みたくない）</t>
+    <rPh sb="1" eb="5">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジガ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長はプレイヤーよりもほんの少し遅くします</t>
+    <rPh sb="0" eb="2">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（捕まらない想定で作ってもらって大丈夫です</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ダイジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制作に余裕があったら校長に捕まった場合も作りたいです）</t>
+    <rPh sb="0" eb="2">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨユウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このシートでは答案怪盗JOKERのコンセプトを書いています</t>
+    <rPh sb="7" eb="9">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンセプト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とある小学校には有名なうわさがあった…</t>
+    <rPh sb="3" eb="6">
+      <t>ショウガッコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ユウメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>難しいテストの答えを盗みに入る怪盗が存在すると…</t>
+    <rPh sb="0" eb="1">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜な夜な学校に忍び込み、テストの答えを盗み出し</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シノ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えを張り出し、なかったことにする</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そんな小学生の味方のような怪盗がいる</t>
+    <rPh sb="3" eb="6">
+      <t>ショウガクセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これはあなたが怪盗になり、テストの回答を盗み出す</t>
+    <rPh sb="7" eb="9">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脱出ゲームです</t>
+    <rPh sb="0" eb="2">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームの名前について</t>
+    <rPh sb="4" eb="6">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さすがに「怪盗」と「JOKER」は怒られる可能性があるのでタイトル画面を作る前に変えます</t>
+    <rPh sb="5" eb="7">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4513,15 +4774,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>29854</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>100578</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>75574</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>15623</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4536,8 +4797,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2346960" y="18478500"/>
-          <a:ext cx="1386840" cy="670560"/>
+          <a:off x="3068561" y="22254334"/>
+          <a:ext cx="1383867" cy="658460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4644,16 +4905,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>61847</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>63407</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>107194</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>127136</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4668,8 +4929,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2331720" y="19850100"/>
-          <a:ext cx="1386840" cy="670560"/>
+          <a:off x="3100554" y="24893456"/>
+          <a:ext cx="1383494" cy="658460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4713,16 +4974,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>61847</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>40547</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>107194</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>104276</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4737,8 +4998,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2331720" y="21198840"/>
-          <a:ext cx="1386840" cy="670560"/>
+          <a:off x="3100554" y="26208742"/>
+          <a:ext cx="1383494" cy="658461"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4791,15 +5052,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>42024</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>117843</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>62406</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>54114</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4810,15 +5071,12 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="70" idx="2"/>
-          <a:endCxn id="74" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3025140" y="19149060"/>
-          <a:ext cx="15240" cy="701040"/>
+          <a:off x="3749804" y="24204477"/>
+          <a:ext cx="20382" cy="679686"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4847,15 +5105,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>79194</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>127136</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>79194</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>40547</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4873,8 +5131,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3025140" y="20520660"/>
-          <a:ext cx="0" cy="678180"/>
+          <a:off x="3786974" y="25551916"/>
+          <a:ext cx="0" cy="656826"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4902,219 +5160,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
-      <xdr:row>147</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>61847</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>25307</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="81" name="フローチャート: 判断 80">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25C650F3-78EE-459A-BA9D-4E3618E6E6F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2316480" y="22433280"/>
-          <a:ext cx="1394460" cy="1104900"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartDecision">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
-            <a:t>特殊問題に正解した？</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>152</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>153</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="82" name="フローチャート: 結合子 81">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E611F8AD-CE49-4A5C-8B0C-5039014DEBE2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3520440" y="23164800"/>
-          <a:ext cx="251460" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartConnector">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>Y</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>147</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="83" name="フローチャート: 結合子 82">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7A3A5F-4CD9-4938-8C33-9C3665CB7053}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3566160" y="22517100"/>
-          <a:ext cx="251460" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartConnector">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>N</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>158</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>107194</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>86269</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5129,8 +5184,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2331720" y="24079200"/>
-          <a:ext cx="1386840" cy="670560"/>
+          <a:off x="3100554" y="29018478"/>
+          <a:ext cx="1383494" cy="655693"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5175,15 +5230,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>71573</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>148212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:colOff>122433</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>60490</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5198,8 +5253,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2346960" y="25473660"/>
-          <a:ext cx="1386840" cy="670560"/>
+          <a:off x="3110280" y="30479529"/>
+          <a:ext cx="1389007" cy="655693"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5243,23 +5298,190 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>158</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>73276</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>104276</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>79194</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>55787</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="88" name="直線矢印コネクタ 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0479CACF-1952-44E0-9767-90328F08D9FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="75" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3781056" y="26867203"/>
+          <a:ext cx="5918" cy="546243"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>73276</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>96656</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>79194</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>25307</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="90" name="直線矢印コネクタ 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D64E3A7-1519-4ADA-BF14-128CDF27B736}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:endCxn id="84" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3781056" y="28495095"/>
+          <a:ext cx="5918" cy="523383"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>79194</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>86269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>99576</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>48167</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="92" name="直線矢印コネクタ 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{118E6976-81FE-443D-8653-125F007CDA6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="84" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3786974" y="29674171"/>
+          <a:ext cx="20382" cy="705313"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>40702</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>146639</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>86422</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>55198</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="86" name="正方形/長方形 85">
+        <xdr:cNvPr id="53" name="正方形/長方形 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{321BC27B-7B7A-4E07-9020-5980D1B30CF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4675DE79-A50B-4C7A-B806-45B7C2E95F53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5267,14 +5489,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4556760" y="24086820"/>
-          <a:ext cx="1386840" cy="670560"/>
+          <a:off x="3079409" y="17988590"/>
+          <a:ext cx="1383867" cy="651974"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent1">
+          <a:schemeClr val="accent2">
             <a:lumMod val="60000"/>
             <a:lumOff val="40000"/>
           </a:schemeClr>
@@ -5303,7 +5525,15 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>ゲームオーバー</a:t>
+            <a:t>職員室で屋上の</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>カギを取りに行く</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5312,35 +5542,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>163830</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>46464</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>65606</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>147</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:colOff>50274</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>96085</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="88" name="直線矢印コネクタ 87">
+        <xdr:cNvPr id="55" name="直線矢印コネクタ 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0479CACF-1952-44E0-9767-90328F08D9FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ED47C79-60D7-4BAC-9DB8-C992FA826BCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="75" idx="2"/>
-          <a:endCxn id="81" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3013710" y="21869400"/>
-          <a:ext cx="11430" cy="563880"/>
+          <a:off x="3754244" y="18650972"/>
+          <a:ext cx="3810" cy="625211"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5368,35 +5595,101 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>163830</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12824</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>75828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>66164</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>113929</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="フローチャート: 判断 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B20EF42D-FA71-4497-A23E-D6660427064E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3051531" y="19255926"/>
+          <a:ext cx="1391487" cy="1078881"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>特殊問題に正解した？</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>37171</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>120804</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>158</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>40981</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>2600</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="90" name="直線矢印コネクタ 89">
+        <xdr:cNvPr id="60" name="直線矢印コネクタ 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D64E3A7-1519-4ADA-BF14-128CDF27B736}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82072E7E-0410-43AC-A1BF-3559332D1B81}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="81" idx="2"/>
-          <a:endCxn id="84" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3013710" y="23538180"/>
-          <a:ext cx="11430" cy="541020"/>
+        <a:xfrm flipH="1">
+          <a:off x="3744951" y="20341682"/>
+          <a:ext cx="3810" cy="625211"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5424,35 +5717,102 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>35126</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>20258</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>80846</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>77501</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="正方形/長方形 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51D872FD-CA46-4A1D-A968-30D7C8CBFE90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3073833" y="20984551"/>
+          <a:ext cx="1383867" cy="651974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>カギ獲得</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>59474</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>68765</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>63284</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>99244</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="92" name="直線矢印コネクタ 91">
+        <xdr:cNvPr id="65" name="直線矢印コネクタ 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{118E6976-81FE-443D-8653-125F007CDA6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D5A7CA-1391-4511-861D-EC7E1E39397F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="84" idx="2"/>
-          <a:endCxn id="85" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3025140" y="24749760"/>
-          <a:ext cx="15240" cy="723900"/>
+        <a:xfrm flipH="1">
+          <a:off x="3767254" y="21627789"/>
+          <a:ext cx="3810" cy="625211"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5480,38 +5840,376 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>150</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>38843</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>70439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>84563</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>127681</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="正方形/長方形 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA6F229E-1FE2-4425-9327-2DE4B64DDC2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3077550" y="23562341"/>
+          <a:ext cx="1383867" cy="651974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>２</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>F</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>へ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>44606</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>35311</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>48416</xdr:colOff>
       <xdr:row>158</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>65791</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="94" name="コネクタ: カギ線 93">
+        <xdr:cNvPr id="67" name="直線矢印コネクタ 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9173AB60-6BC4-44AA-9F85-CC3FE886B4AC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80064681-E73F-462E-84F0-005727EAA205}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3752386" y="22932482"/>
+          <a:ext cx="3810" cy="625211"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>93442</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>100021</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>138789</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>15067</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="正方形/長方形 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D463D29D-B28D-43C0-BBFD-CE3F0E90C5F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3132149" y="27606362"/>
+          <a:ext cx="1383494" cy="658461"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>屋上のカギを開ける</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>82148</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>102219</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>165969</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>60216</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="71" name="フローチャート: 結合子 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1411190-308C-4BF6-82FD-904C2A27E4AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4124465" y="20025731"/>
+          <a:ext cx="251089" cy="255363"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>82520</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>120804</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>166339</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>78802</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="フローチャート: 結合子 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA5C3641-4387-4386-AFE0-267A613DBF76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4292105" y="19300902"/>
+          <a:ext cx="251088" cy="255363"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>N</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>39495</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>75828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>66164</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>20538</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="コネクタ: カギ線 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663C854F-12C9-491D-920C-39574376E00F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="81" idx="3"/>
-          <a:endCxn id="86" idx="0"/>
+          <a:stCxn id="58" idx="3"/>
+          <a:endCxn id="58" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3710940" y="22985730"/>
-          <a:ext cx="1539240" cy="1101090"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="3747275" y="19255926"/>
+          <a:ext cx="695743" cy="539441"/>
         </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -32857"/>
+            <a:gd name="adj2" fmla="val 142377"/>
+          </a:avLst>
         </a:prstGeom>
         <a:ln w="38100">
           <a:tailEnd type="triangle"/>
@@ -5833,6 +6531,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C78DD1D-452A-4AC7-BC27-DE6E75E1AF27}">
+  <dimension ref="K1:K16"/>
+  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K4" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K14" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FC5186-FD62-4BC4-B6C2-9C2D8535B64D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C43A3-048F-4D64-AC47-FC3BA283DCF5}">
   <dimension ref="A1:Q89"/>
   <sheetFormatPr defaultColWidth="5.59765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -6124,12 +6903,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C47E4FE-46DD-4F08-9A2A-B0D71841B40D}">
   <dimension ref="A1:AI56"/>
   <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -6309,12 +7088,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="50" spans="13:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M50" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="13:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M51" t="s">
         <v>150</v>
       </c>
@@ -6322,22 +7101,25 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="13:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="P52" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="54" spans="13:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M54" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="13:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="5">
+        <v>45953</v>
+      </c>
       <c r="M55" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="13:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M56" t="s">
         <v>155</v>
       </c>
@@ -6348,9 +7130,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643C8F94-237C-4F52-86C7-FE7033AFCF0B}">
-  <dimension ref="A1:AR71"/>
+  <dimension ref="A1:AR75"/>
   <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
@@ -6674,6 +7456,21 @@
         <v>154</v>
       </c>
     </row>
+    <row r="73" spans="10:10" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J73" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J74" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J75" t="s">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6681,9 +7478,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C73B12-1CE8-46A3-9E46-0FBD29283B60}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:AA181"/>
   <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
@@ -6710,6 +7507,21 @@
         <v>157</v>
       </c>
     </row>
+    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Z179" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Z180" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AA181" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
+++ b/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\制作物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ACD6E8-AECC-451D-B742-525C54790970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3730139D-FEE1-4F22-BC0C-7609998B89EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
   </bookViews>
   <sheets>
     <sheet name="コンセプト" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="イベント" sheetId="3" r:id="rId5"/>
     <sheet name="フローチャート" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,648 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="251">
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンセプト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とある小学校には有名なうわさがあった…</t>
+    <rPh sb="3" eb="6">
+      <t>ショウガッコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ユウメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>難しいテストの答えを盗みに入る怪盗が存在すると…</t>
+    <rPh sb="0" eb="1">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜な夜な学校に忍び込み、テストの答えを盗み出し</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シノ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えを張り出し、なかったことにする</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そんな小学生の味方のような怪盗がいる</t>
+    <rPh sb="3" eb="6">
+      <t>ショウガクセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これはあなたが怪盗になり、テストの回答を盗み出す</t>
+    <rPh sb="7" eb="9">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脱出ゲームです</t>
+    <rPh sb="0" eb="2">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームの名前について</t>
+    <rPh sb="4" eb="6">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さすがに「怪盗」と「JOKER」は怒られる可能性があるのでタイトル画面を作る前に変えます</t>
+    <rPh sb="5" eb="7">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（難しいテストを行わせない、実際の義賊のような感じ、小学生からは人気みたいな）</t>
+    <rPh sb="1" eb="2">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ギゾク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ショウガクセイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ニンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンサーと盗む（スティール）、スクールの組みあわせ</t>
+    <rPh sb="5" eb="6">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽室</t>
+    <rPh sb="0" eb="3">
+      <t>オンガクシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左上（ピアノ）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>☆</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左下（楽器たち）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリシタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央上（指揮台）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央下（机といす）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツクエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右上ロッカー</t>
+    <rPh sb="0" eb="2">
+      <t>ミギウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右下（本棚）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室</t>
+    <rPh sb="0" eb="3">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左（水道）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央（校長の彫像、校長登場の伏線用）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウゾウ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>コウチョウトウジョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フクセン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>彫像を囲うもの（イーゼルといす）</t>
+    <rPh sb="0" eb="2">
+      <t>チョウゾウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右上（美術の本棚）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギウエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ビジュツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右下（デッサンの本棚）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科室</t>
+    <rPh sb="0" eb="3">
+      <t>リカシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左上（人体模型）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ジンタイモケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左下（ロッカー）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリシタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央（机といす）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツクエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右上（本棚、ヒントがあります）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギウエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右中央（水道と教卓）</t>
+    <rPh sb="0" eb="3">
+      <t>ミギチュウオウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>スイドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右下（実験物を流す専用の水道）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ジッケンブツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左側の石（図書カウンター）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本棚（ヒントを置く）</t>
+    <rPh sb="0" eb="2">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カウンター上の本棚（社会のヒント）</t>
+    <rPh sb="5" eb="6">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右から2列目上の本棚（国語のヒント）</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コクゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１F廊下</t>
+    <rPh sb="2" eb="4">
+      <t>ロウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一番左の茶色のドア（職員室）</t>
+    <rPh sb="0" eb="3">
+      <t>イチバンヒダリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ショクインシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白い手前のドアたち（教室）</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テマエ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白い奥のドア（理科室）</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>リカシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥の茶色のドア（図書室）</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>トショシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>階段横（地図）</t>
+    <rPh sb="0" eb="3">
+      <t>カイダンヨコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２F廊下</t>
+    <rPh sb="2" eb="4">
+      <t>ロウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左の茶色ドア（校長室）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下の白いドア（教室）</t>
+    <rPh sb="0" eb="1">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥の白いドア（音楽室）</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>オンガクシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右のちょっと茶色ドア（美術室）</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左右端の台（地図）</t>
+    <rPh sb="0" eb="3">
+      <t>サユウハシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長室</t>
+  </si>
+  <si>
+    <t>真ん中（机といす、来客用）</t>
+  </si>
+  <si>
+    <t>下（校長の机、パソコンと電話とナポリタンを置く）</t>
+  </si>
+  <si>
+    <t>机に注目したとき</t>
+  </si>
+  <si>
+    <t>シナリオに記載</t>
+  </si>
+  <si>
+    <t>一般教室</t>
+  </si>
+  <si>
+    <t>すべて教室はこのつくりでOK</t>
+  </si>
+  <si>
+    <t>左　教卓</t>
+  </si>
+  <si>
+    <t>一番右　ロッカー</t>
+  </si>
+  <si>
+    <t>廊下はスクロール式にする</t>
+  </si>
   <si>
     <t>更新日</t>
     <rPh sb="0" eb="3">
@@ -71,13 +712,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>概要</t>
-    <rPh sb="0" eb="2">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>このページでは答案回答JOKERの仕様について書いています</t>
     <rPh sb="7" eb="11">
       <t>トウアンカイトウ</t>
@@ -174,6 +808,25 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>校内には見回りの先生が徘徊しているので見つからないようにします</t>
+    <rPh sb="0" eb="2">
+      <t>コウナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハイカイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>校内に答案があるので見つけて学校から脱出すればクリアとなります</t>
     <rPh sb="0" eb="2">
       <t>コウナイ</t>
@@ -212,6 +865,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>問題は四択で出します</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨンタク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>それぞれ答案がある場所で教科に沿った問題に答えてもらいます</t>
     <rPh sb="4" eb="6">
       <t>トウアン</t>
@@ -260,19 +926,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>問題は四択で出します</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨンタク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>１．人間失格</t>
     <rPh sb="2" eb="6">
       <t>ニンゲンシッカク</t>
@@ -333,21 +986,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>校内には見回りの先生が徘徊しているので見つからないようにします</t>
-    <rPh sb="0" eb="2">
-      <t>コウナイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ミマワ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ハイカイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ミ</t>
+    <t>制限時間なしに変更、間違えたら捕まるようにします</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -443,7 +1093,30 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>マップとプレイヤーの大きさ、当たり判定について</t>
+    <rPh sb="10" eb="11">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>このゲームは１マス３２＊３２となっています</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1マス６４＊６４に変更（粗くなりすぎたため）</t>
+    <rPh sb="9" eb="11">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アラ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -454,6 +1127,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>プレイヤーは64＊64とする（１マスのところをとおれるようにするため）</t>
+  </si>
+  <si>
     <t>廊下の大きさ　５＊５６</t>
     <rPh sb="0" eb="2">
       <t>ロウカ</t>
@@ -464,31 +1140,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>図書室　理科室　音楽室　美術室の大きさ　１５＊２５</t>
-    <rPh sb="0" eb="2">
-      <t>トショ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シツ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ビジュツ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>シツ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>オオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>教室　校長室の大きさ　１２＊１２</t>
     <rPh sb="0" eb="2">
       <t>キョウシツ</t>
@@ -505,6 +1156,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>図書室　　１５＊２５　理科室、美術室、音楽室　縦１５　横２０</t>
+  </si>
+  <si>
     <t>マップのイメージはマインクラフトサーバーを参照すること</t>
     <rPh sb="21" eb="23">
       <t>サンショウ</t>
@@ -512,19 +1166,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>マップとプレイヤーの大きさ、当たり判定について</t>
-    <rPh sb="10" eb="11">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>当たり判定</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
@@ -548,7 +1189,61 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>判定はプレイヤーの体の外側と先生の正面足元に当たった時とする</t>
+    <rPh sb="0" eb="2">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カラダ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソトガワ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウメン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>アシモト</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（青鬼と同じ感じ）</t>
+    <rPh sb="1" eb="3">
+      <t>アオオニ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>マップのイベントについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案の場所の変更</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -580,6 +1275,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>イベントシートの答案の場所に記載</t>
+    <rPh sb="8" eb="10">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>図書室には４択問題のヒントが置かれています</t>
     <rPh sb="0" eb="3">
       <t>トショシツ</t>
@@ -615,7 +1323,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>イベントが発生する（本や隠し場所）では！を表示する</t>
+    <t>イベントが発生する（本や隠し場所）では！を表示する（ドアを開けるときも）</t>
     <rPh sb="5" eb="7">
       <t>ハッセイ</t>
     </rPh>
@@ -627,6 +1335,9 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -641,18 +1352,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>（プレイヤーに分かりやすいようにしたいので、！の横や下にSPACEと表示できればしたいです）</t>
+    <t>（プレイヤーに分かりやすいようにしたいので、キャラクターの上に！を表示して何かできることをわかりやすくしたいです）</t>
     <rPh sb="7" eb="8">
       <t>ワ</t>
     </rPh>
-    <rPh sb="24" eb="25">
-      <t>ヨコ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
+    <rPh sb="29" eb="30">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
       <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ナニ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -735,6 +1446,42 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>SEやBGM、素材について</t>
+  </si>
+  <si>
+    <t>BGMは作る予定です（できなかったらフリー素材のやつを使います）</t>
+  </si>
+  <si>
+    <t>SEはフリー音源を使えるサイトがあるのでそこから使ってください</t>
+  </si>
+  <si>
+    <t>サイトURL</t>
+  </si>
+  <si>
+    <t>https://soundeffect-lab.info/</t>
+  </si>
+  <si>
+    <t>色々な素材（イラストなど）は下にサイトを載せるので使ってください</t>
+  </si>
+  <si>
+    <t>https://dot-illust.net/</t>
+  </si>
+  <si>
+    <t>←このサイトは３０種類まで無料で使えます</t>
+  </si>
+  <si>
+    <t>これ以外にもフリー素材は使って大丈夫ですが</t>
+  </si>
+  <si>
+    <t>利用規約は守ってください</t>
+  </si>
+  <si>
+    <t>マップと当たり判定をとりあえず作ってください</t>
+  </si>
+  <si>
+    <t>その際プレイヤーは葵ちゃんで代用してください</t>
+  </si>
+  <si>
     <t>更新内容</t>
     <rPh sb="0" eb="4">
       <t>コウシンナイヨウ</t>
@@ -954,6 +1701,388 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>答案以外のイベントについて</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教室の！が発生している場所</t>
+    <rPh sb="0" eb="2">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（答案のない教室にも机１つ、ロッカー一つに！を付けて探せるようにしたいです）</t>
+    <rPh sb="1" eb="3">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：机を開けた場合</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「机を探した　しかしなにもなかった」</t>
+    <rPh sb="1" eb="2">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロッカーを開けた場合</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ロッカーを探した　しかしなにもなかった」</t>
+    <rPh sb="6" eb="7">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科室の教卓に置いてある教科書</t>
+    <rPh sb="0" eb="3">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョウタク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>キョウカショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「火が燃えるには酸素が必要不可欠！覚えておこう！」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サンソ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>ヒツヨウフカケツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室の校長の彫像</t>
+    <rPh sb="0" eb="3">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チョウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「校長先生の彫像らしい…　筋肉ムキムキだ」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>コウチョウセンセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チョウゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キンニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室の本棚</t>
+    <rPh sb="0" eb="3">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「イラストの本しかないようだ…」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽室の楽譜棚</t>
+    <rPh sb="0" eb="3">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガクフ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　楽譜が並んでいる…　全く読めない」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガクフ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マッタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽室のピアノ</t>
+    <rPh sb="0" eb="3">
+      <t>オンガクシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「立派なグランドピアノだ」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リッパ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長室の好物（校長の机の上にある）</t>
+    <rPh sb="0" eb="3">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「ナポリタンが…？　あまりいい気分ではない」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屋上に入るとき</t>
+    <rPh sb="0" eb="2">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「屋上はカギがかけられている…」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オクジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題に挑戦しますか？</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案の場所で問題に答えるとき</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「？にはカギがかけられている…」　</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（最初の？にはロッカーや引き出しが入る）</t>
+    <rPh sb="1" eb="3">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長の出現条件について</t>
+    <rPh sb="0" eb="2">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>シュツゲンジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長は４つの回答を集め、屋上に向かうフェーズに入った時に登場する</t>
+    <rPh sb="0" eb="2">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追いかけてくる場所は屋上の問題を解く場所までとする</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>この仕様書はイベントについての仕様書です</t>
     <rPh sb="2" eb="5">
       <t>シヨウショ</t>
@@ -1108,6 +2237,28 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>ロッカーや机の中を探す時も！を表示して探せることをわかりやすくしたいです</t>
+    <rPh sb="5" eb="6">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>答案の発生場所について</t>
     <rPh sb="0" eb="2">
       <t>トウアン</t>
@@ -1128,28 +2279,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ロッカーや机の中を探す時も！を表示して探せることをわかりやすくしたいです</t>
-    <rPh sb="5" eb="6">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>サガ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>図書室を除く理科室など名前の付いた部屋にランダム２つで出現させます</t>
     <rPh sb="0" eb="3">
       <t>トショシツ</t>
@@ -1175,6 +2304,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>ランダムではなく固定沸きにしてバグが起こらないようにする</t>
+    <rPh sb="8" eb="10">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>（図書室には全部ではなくとも４択のヒントを置きたいです）</t>
     <rPh sb="1" eb="4">
       <t>トショシツ</t>
@@ -1302,6 +2444,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>特別問題について</t>
+    <rPh sb="0" eb="4">
+      <t>トクベツモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>国語　</t>
     <rPh sb="0" eb="2">
       <t>コクゴ</t>
@@ -1309,6 +2458,73 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>屋上から脱出するための問題についてです</t>
+    <rPh sb="0" eb="2">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダッシュツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長室の中にある校長の好物が答えになります</t>
+    <rPh sb="0" eb="3">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナポリタンが好物</t>
+    <rPh sb="6" eb="8">
+      <t>コウブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屋上特別問題</t>
+    <rPh sb="0" eb="2">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>トクベツモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長先生の好物は？</t>
+    <rPh sb="0" eb="4">
+      <t>コウチョウセンセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．ちくわ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．ユッケ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>算数　</t>
     <rPh sb="0" eb="2">
       <t>サンスウ</t>
@@ -1320,7 +2536,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>３．ナポリタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>1.　６</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．鮭おにぎり</t>
+    <rPh sb="2" eb="3">
+      <t>シャケ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1448,19 +2675,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ランダムではなく固定沸きにしてバグが起こらないようにする</t>
-    <rPh sb="8" eb="10">
-      <t>コテイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>答案の置き場所について</t>
     <rPh sb="0" eb="2">
       <t>トウアン</t>
@@ -1515,80 +2729,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>特別問題について</t>
-    <rPh sb="0" eb="4">
-      <t>トクベツモンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>屋上から脱出するための問題についてです</t>
-    <rPh sb="0" eb="2">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ダッシュツ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>モンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長室の中にある校長の好物が答えになります</t>
-    <rPh sb="0" eb="3">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウブツ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>屋上特別問題</t>
-    <rPh sb="0" eb="2">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>トクベツモンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長先生の好物は？</t>
-    <rPh sb="0" eb="4">
-      <t>コウチョウセンセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．せんべい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．ユッケ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．鮭おにぎり</t>
-    <rPh sb="2" eb="3">
-      <t>シャケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>理科：理科室の人体模型</t>
     <rPh sb="0" eb="2">
       <t>リカ</t>
@@ -1602,459 +2742,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>判定はプレイヤーの体の外側と先生の正面足元に当たった時とする</t>
-    <rPh sb="0" eb="2">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カラダ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ソトガワ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ショウメン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>アシモト</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>トキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（青鬼と同じ感じ）</t>
-    <rPh sb="1" eb="3">
-      <t>アオオニ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案以外のイベントについて</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イガイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>教室の！が発生している場所</t>
-    <rPh sb="0" eb="2">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：机を開けた場合</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「机を探した　しかしなにもなかった」</t>
-    <rPh sb="1" eb="2">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロッカーを開けた場合</t>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「ロッカーを探した　しかしなにもなかった」</t>
-    <rPh sb="6" eb="7">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（答案のない教室にも机１つ、ロッカー一つに！を付けて探せるようにしたいです）</t>
-    <rPh sb="1" eb="3">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>理科室の教卓に置いてある教科書</t>
-    <rPh sb="0" eb="3">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キョウタク</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>キョウカショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「火が燃えるには酸素が必要不可欠！覚えておこう！」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>サンソ</t>
-    </rPh>
-    <rPh sb="14" eb="19">
-      <t>ヒツヨウフカケツ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>美術室の校長の彫像</t>
-    <rPh sb="0" eb="3">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>チョウゾウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「校長先生の彫像らしい…　筋肉ムキムキだ」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>コウチョウセンセイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チョウゾウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>キンニク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イベントシートの答案の場所に記載</t>
-    <rPh sb="8" eb="10">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案の場所の変更</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>美術室の本棚</t>
-    <rPh sb="0" eb="3">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホンダナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「イラストの本しかないようだ…」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音楽室の楽譜棚</t>
-    <rPh sb="0" eb="3">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガクフ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>タナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　楽譜が並んでいる…　全く読めない」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガクフ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ナラ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>マッタ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音楽室のピアノ</t>
-    <rPh sb="0" eb="3">
-      <t>オンガクシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「立派なグランドピアノだ」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>リッパ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホルモン焼きが好物</t>
-    <rPh sb="4" eb="5">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．ホルモン焼き</t>
-    <rPh sb="6" eb="7">
-      <t>ヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長室の好物（校長の机の上にある）</t>
-    <rPh sb="0" eb="3">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウブツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ウエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「何でここにホルモン焼きが…？　大量に作られている」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ナン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>タイリョウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>屋上に入るとき</t>
-    <rPh sb="0" eb="2">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「屋上はカギがかけられている…」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>オクジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>問題に挑戦しますか？</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>チョウセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案の場所で問題に答えるとき</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「？にはカギがかけられている…」　</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（最初の？にはロッカーや引き出しが入る）</t>
-    <rPh sb="1" eb="3">
-      <t>サイショ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長の出現条件について</t>
-    <rPh sb="0" eb="2">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>シュツゲンジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長は４つの回答を集め、屋上に向かうフェーズに入った時に登場する</t>
-    <rPh sb="0" eb="2">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>トウジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>社会：2階校長室隣の教室の教卓</t>
     <rPh sb="0" eb="2">
       <t>シャカイ</t>
@@ -2077,24 +2764,53 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>追いかけてくる場所は屋上の問題を解く場所までとする</t>
-    <rPh sb="0" eb="1">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バショ</t>
+    <t>特殊問題について</t>
+    <rPh sb="0" eb="4">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特殊問題（職員室で獲得するカギ）は間違えても見回りの先生に捕まらない（ゲームオーバーにならない）とする</t>
+    <rPh sb="0" eb="4">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ショクインシツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（特殊問題はこっちの自我で作ってるので、プレイヤーを巻き込みたくない）</t>
+    <rPh sb="1" eb="5">
+      <t>トクシュモンダイ</t>
     </rPh>
     <rPh sb="10" eb="12">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>バショ</t>
+      <t>ジガ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2106,10 +2822,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>フローチャート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>フローチャート設定</t>
     <rPh sb="7" eb="9">
       <t>セッテイ</t>
@@ -2117,54 +2829,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>特殊問題について</t>
-    <rPh sb="0" eb="4">
-      <t>トクシュモンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特殊問題（職員室で獲得するカギ）は間違えても見回りの先生に捕まらない（ゲームオーバーにならない）とする</t>
-    <rPh sb="0" eb="4">
-      <t>トクシュモンダイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ショクインシツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ミマワ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（特殊問題はこっちの自我で作ってるので、プレイヤーを巻き込みたくない）</t>
-    <rPh sb="1" eb="5">
-      <t>トクシュモンダイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジガ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>コ</t>
-    </rPh>
+    <t>フローチャート</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2219,160 +2884,149 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>このシートでは答案怪盗JOKERのコンセプトを書いています</t>
+    <t>教室は全体を映して大丈夫です</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウツ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ダイジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦5マス　横５６マス</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦５　横５６</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦　１２　横１２</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦１２　横１２</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦１５　横２５</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦１５　横２０</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦　１５　横２０</t>
+    <rPh sb="0" eb="1">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（当たり判定などは青鬼のようにしたいですが、壁と重なったり、ゲーム上なんかおかしいなどあったら</t>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>アオオニ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラマーの方でいい感じにしてくれると助かります）</t>
+    <rPh sb="7" eb="8">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このシートでは答案怪盗JOKER（仮）のコンセプトを書いています</t>
     <rPh sb="7" eb="9">
       <t>トウアン</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="23" eb="24">
+    <rPh sb="17" eb="18">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
       <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コンセプト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>とある小学校には有名なうわさがあった…</t>
-    <rPh sb="3" eb="6">
-      <t>ショウガッコウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ユウメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>難しいテストの答えを盗みに入る怪盗が存在すると…</t>
-    <rPh sb="0" eb="1">
-      <t>ムズカ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ヌス</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
+    <t>【答案怪盗アスター】に変更します</t>
+    <rPh sb="1" eb="3">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="18" eb="20">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>夜な夜な学校に忍び込み、テストの答えを盗み出し</t>
-    <rPh sb="0" eb="1">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガッコウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>シノ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヌス</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答えを張り出し、なかったことにする</t>
-    <rPh sb="0" eb="1">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ハ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そんな小学生の味方のような怪盗がいる</t>
-    <rPh sb="3" eb="6">
-      <t>ショウガクセイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カイトウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>これはあなたが怪盗になり、テストの回答を盗み出す</t>
-    <rPh sb="7" eb="9">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ヌス</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>脱出ゲームです</t>
-    <rPh sb="0" eb="2">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームの名前について</t>
-    <rPh sb="4" eb="6">
-      <t>ナマエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>さすがに「怪盗」と「JOKER」は怒られる可能性があるのでタイトル画面を作る前に変えます</t>
-    <rPh sb="5" eb="7">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>オコ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>カノウセイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>カ</t>
+    <rPh sb="11" eb="13">
+      <t>ヘンコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2381,7 +3035,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2401,6 +3055,15 @@
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -2436,12 +3099,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2463,8 +3129,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2481,6 +3151,471 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>671514</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>176213</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>130968</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B731E2-96BC-4D97-8744-BFBB605D07A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="671514" y="233362"/>
+          <a:ext cx="4991099" cy="2807494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>646340</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>113392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>623661</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>73391</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01E2AF10-576C-4608-9B13-CAA970674FB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="646340" y="5329463"/>
+          <a:ext cx="5420178" cy="3588571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>656140</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>40368</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>515015</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>75867</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C1B89B8-C045-4217-B644-94C62237E190}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="656140" y="10451415"/>
+          <a:ext cx="6039049" cy="3358173"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>11074</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>204898</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>620233</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>88110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA77172F-5326-4E80-8137-91C9256071C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="697760" y="15267689"/>
+          <a:ext cx="6102647" cy="3427398"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>681148</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>88604</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>70662</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>160596</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE653C8B-6B43-4700-AC01-2FCC27FCE77B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="681148" y="20024651"/>
+          <a:ext cx="7629747" cy="2065596"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>116294</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>94144</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>230594</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>25032</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD8D51E-6166-462C-8F36-1C0602458345}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="116294" y="23795888"/>
+          <a:ext cx="10414591" cy="1924493"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEE246AD-433B-10C8-1F37-7296F975B44E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2DD8D51E-6166-462C-8F36-1C0602458345}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="26727150"/>
+          <a:ext cx="5400675" cy="5133975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5366430-7CA6-FD8F-490F-B62482B3CA14}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BEE246AD-433B-10C8-1F37-7296F975B44E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="714375" y="32632650"/>
+          <a:ext cx="5457825" cy="5238750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2535,7 +3670,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6532,367 +7667,396 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C78DD1D-452A-4AC7-BC27-DE6E75E1AF27}">
-  <dimension ref="K1:K16"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="K1:K19"/>
+  <sheetFormatPr defaultColWidth="2.25" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K4" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="K2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="K4" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="K5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="K6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K9" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K14" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K16" t="s">
-        <v>175</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K19" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FC5186-FD62-4BC4-B6C2-9C2D8535B64D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C43A3-048F-4D64-AC47-FC3BA283DCF5}">
-  <dimension ref="A1:Q89"/>
-  <sheetFormatPr defaultColWidth="5.59765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="10.796875" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="B3:Q177"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E12" t="s">
+    <row r="3" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="10:12" x14ac:dyDescent="0.7">
+      <c r="J10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E16" t="s">
+    <row r="27" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="5:7" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E31" s="3" t="s">
+    <row r="28" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E32" t="s">
+    <row r="29" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K29" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="34" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E34" t="s">
+      <c r="O29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K30" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E35" t="s">
+      <c r="O30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="11:15" x14ac:dyDescent="0.7">
+      <c r="K31" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L49" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E36" t="s">
+    <row r="50" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L50" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="N38" t="s">
+      <c r="N50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L51" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="5:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E55" s="3" t="s">
+    <row r="52" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L53" t="s">
+        <v>31</v>
+      </c>
+      <c r="O53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="12:15" x14ac:dyDescent="0.7">
+      <c r="L56" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="12:16" x14ac:dyDescent="0.7">
+      <c r="L71" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="12:16" x14ac:dyDescent="0.7">
+      <c r="L72" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="12:16" x14ac:dyDescent="0.7">
+      <c r="L73" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="56" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E56" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E57" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E59" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E60" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E61" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E63" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E65" t="s">
+      <c r="P73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="12:16" x14ac:dyDescent="0.7">
+      <c r="L74" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E67" t="s">
+      <c r="P74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="12:16" x14ac:dyDescent="0.7">
+      <c r="L75" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="92" spans="14:14" x14ac:dyDescent="0.7">
+      <c r="N92" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E68" t="s">
-        <v>121</v>
-      </c>
-      <c r="O68" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E70" s="3" t="s">
+    <row r="93" spans="14:14" x14ac:dyDescent="0.7">
+      <c r="N93" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B72" t="s">
-        <v>135</v>
-      </c>
-      <c r="E72" s="6" t="s">
+    <row r="94" spans="14:14" x14ac:dyDescent="0.7">
+      <c r="N94" t="s">
         <v>40</v>
       </c>
-      <c r="Q72" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E74" t="s">
+    </row>
+    <row r="95" spans="14:14" x14ac:dyDescent="0.7">
+      <c r="N95" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E75" t="s">
+    <row r="96" spans="14:14" x14ac:dyDescent="0.7">
+      <c r="N96" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E77" t="s">
+    <row r="97" spans="14:17" x14ac:dyDescent="0.7">
+      <c r="N97" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E78" t="s">
+    <row r="98" spans="14:17" x14ac:dyDescent="0.7">
+      <c r="N98" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109" spans="14:17" x14ac:dyDescent="0.7">
+      <c r="Q109" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E79" t="s">
+    <row r="110" spans="14:17" x14ac:dyDescent="0.7">
+      <c r="Q110" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E81" t="s">
+    <row r="111" spans="14:17" x14ac:dyDescent="0.7">
+      <c r="Q111" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E82" t="s">
+    <row r="112" spans="14:17" x14ac:dyDescent="0.7">
+      <c r="Q112" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E84" t="s">
+    <row r="113" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="Q113" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="86" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="4">
-        <v>45951</v>
-      </c>
-      <c r="E86" s="3" t="s">
+    <row r="114" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="Q114" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E88" t="s">
+    <row r="115" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="Q115" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="K124" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E89" t="s">
+    <row r="125" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="K125" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="126" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="K126" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="127" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="K127" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="128" spans="11:17" x14ac:dyDescent="0.7">
+      <c r="K128" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="129" spans="11:11" x14ac:dyDescent="0.7">
+      <c r="K129" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="150" spans="11:11" x14ac:dyDescent="0.7">
+      <c r="K150" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="151" spans="11:11" x14ac:dyDescent="0.7">
+      <c r="K151" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="152" spans="11:11" x14ac:dyDescent="0.7">
+      <c r="K152" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="153" spans="11:11" x14ac:dyDescent="0.7">
+      <c r="K153" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="154" spans="11:11" x14ac:dyDescent="0.7">
+      <c r="K154" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B176" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B177" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -6903,225 +8067,609 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C43A3-048F-4D64-AC47-FC3BA283DCF5}">
+  <dimension ref="A1:Q108"/>
+  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E10" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="G21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="G24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A28" s="5">
+        <v>45961</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="P28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E31" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="N38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E55" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A56" s="5">
+        <v>45958</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E57" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M57" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E60" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E61" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E63" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E67" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E68" t="s">
+        <v>101</v>
+      </c>
+      <c r="O68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E70" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A72" s="5">
+        <v>45951</v>
+      </c>
+      <c r="B72" t="s">
+        <v>104</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E74" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E75" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E81" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E82" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E84" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A86" s="4">
+        <v>45951</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E88" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E89" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E91" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E92" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E93" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E94" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E95" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E97" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E98" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="99" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E99" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H99" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="101" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E101" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="102" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E102" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E105" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="106" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E106" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="107" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E107" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="108" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E108" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E95" r:id="rId1" xr:uid="{8342DC88-1BA5-4642-9264-5231AFD2F0D1}"/>
+    <hyperlink ref="E99" r:id="rId2" xr:uid="{8D248A31-06D0-4209-A5A0-3C70DC7E6D84}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C47E4FE-46DD-4F08-9A2A-B0D71841B40D}">
   <dimension ref="A1:AI56"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A4" s="4">
         <v>45951</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="13:35" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="13:35" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M18" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M20" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="AI20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="P25" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M27" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="28" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M28" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M34" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M35" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M38" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M43" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M46" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="P48" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M50" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M51" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="AE51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="P52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M54" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A55" s="5">
         <v>45953</v>
       </c>
       <c r="M55" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M56" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -7133,342 +8681,342 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643C8F94-237C-4F52-86C7-FE7033AFCF0B}">
   <dimension ref="A1:AR75"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.3984375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="2.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="2.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A4" s="4">
         <v>45951</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J22" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J23" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J24" s="6" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="AO24" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="4">
         <v>45952</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J30" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="10:44" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="10:44" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J34" s="3" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="AK34" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J35" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="N35" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="AK35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O36" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="AK36" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O37" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="AK37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O39" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="AK39" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="AR39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M41" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AR41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="AR42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J43" t="s">
-        <v>89</v>
+        <v>204</v>
       </c>
       <c r="N43" t="s">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="AR43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O44" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="AR44" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J49" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="N49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O51" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="53" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O53" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J55" t="s">
-        <v>101</v>
+        <v>218</v>
       </c>
       <c r="N55" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O57" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O58" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="59" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O59" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O60" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="61" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="Y61" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="63" spans="10:25" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="63" spans="10:25" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J63" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="65" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J65" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="67" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="67" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J67" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="69" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J69" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J71" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="73" spans="10:10" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="73" spans="10:10" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J73" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="74" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J74" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="75" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J75" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -7481,45 +9029,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C73B12-1CE8-46A3-9E46-0FBD29283B60}">
   <dimension ref="A1:AA181"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.25" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K3" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A16" s="4">
         <v>45952</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="Z179" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="Z180" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="AA181" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
+++ b/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\制作物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3730139D-FEE1-4F22-BC0C-7609998B89EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C264F81E-5CAA-421A-A762-80CE16FE5F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
   </bookViews>
   <sheets>
     <sheet name="コンセプト" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="イベント" sheetId="3" r:id="rId5"/>
     <sheet name="フローチャート" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="237">
+  <si>
+    <t>更新日</t>
+    <rPh sb="0" eb="3">
+      <t>コウシンビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変更者</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンコウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案回答JOKER仕様</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -51,6 +78,2088 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>このページでは答案回答JOKERの仕様について書いています</t>
+    <rPh sb="7" eb="11">
+      <t>トウアンカイトウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目的</t>
+    <rPh sb="0" eb="2">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>若きクリエーター展に向けた５分程度のカジュアル謎解きゲームを作る</t>
+    <rPh sb="0" eb="1">
+      <t>ワカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>フンテイド</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナゾト</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜の学校からテストの答えを盗む現実では味わえない体験をしてもらう</t>
+    <rPh sb="0" eb="1">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンジツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>タイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細仕様</t>
+    <rPh sb="0" eb="4">
+      <t>ショウサイシヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案回答JOKERは夜の学校に侵入して答案を盗むゲームです</t>
+    <rPh sb="0" eb="4">
+      <t>トウアンカイトウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シンニュウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヌス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校内に答案があるので見つけて学校から脱出すればクリアとなります</t>
+    <rPh sb="0" eb="2">
+      <t>コウナイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案は国語　算数　理科　社会　の４つあります</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コクゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれ答案がある場所で教科に沿った問題に答えてもらいます</t>
+    <rPh sb="4" eb="6">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ソ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：国語</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コクゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この中で芥川龍之介が描いた本は？</t>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>アクタガワリュウノスケ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題は四択で出します</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨンタク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．人間失格</t>
+    <rPh sb="2" eb="6">
+      <t>ニンゲンシッカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．こころ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．羅生門</t>
+    <rPh sb="2" eb="5">
+      <t>ラショウモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．雨にも負けず</t>
+    <rPh sb="2" eb="3">
+      <t>アメ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答え：３．羅生門</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ラショウモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題は２０秒以内に回答しないと見回りの先生に捕まってしまいます</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ビョウイナイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校内には見回りの先生が徘徊しているので見つからないようにします</t>
+    <rPh sb="0" eb="2">
+      <t>コウナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハイカイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ内にヒントを置くので活用して問題に挑んでもらいたいです</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>イド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップは廊下　教室　図書室　理科室　音楽室　美術室　校長室　（屋上）があります</t>
+    <rPh sb="4" eb="6">
+      <t>ロウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>トショシツ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>オクジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップの表示について</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップは若干斜めから見えているように表示します</t>
+    <rPh sb="4" eb="6">
+      <t>ジャッカン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（イラストむずかったり、プログラムがむずくなったら見下ろしに変えます）</t>
+    <rPh sb="25" eb="27">
+      <t>ミオ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このゲームは１マス３２＊３２となっています</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーは４８＊３２で表示します</t>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>廊下の大きさ　５＊５６</t>
+    <rPh sb="0" eb="2">
+      <t>ロウカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図書室　理科室　音楽室　美術室の大きさ　１５＊２５</t>
+    <rPh sb="0" eb="2">
+      <t>トショ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ビジュツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教室　校長室の大きさ　１２＊１２</t>
+    <rPh sb="0" eb="2">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップのイメージはマインクラフトサーバーを参照すること</t>
+    <rPh sb="21" eb="23">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップとプレイヤーの大きさ、当たり判定について</t>
+    <rPh sb="10" eb="11">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーと先生がぶつかったとき、プレイヤーは先生に捕まる</t>
+    <rPh sb="6" eb="8">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップのイベントについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案は音楽室と理科室に固定で出現させ、残りは教室にランダムで生成します</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図書室には４択問題のヒントが置かれています</t>
+    <rPh sb="0" eb="3">
+      <t>トショシツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>階段横にマップ地図を設置してプレイヤーが迷子にならないようにします</t>
+    <rPh sb="0" eb="2">
+      <t>カイダン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨコ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チズ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベントはSPACEを押すことで始められる</t>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒント本を開いたときは文字を表示します</t>
+    <rPh sb="3" eb="4">
+      <t>ボン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：芥川龍之介　代表作：羅生門</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>アクタガワ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リュウノスケ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ダイヒョウサク</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ラショウモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒントは何度も開けるようにしたいです</t>
+    <rPh sb="4" eb="6">
+      <t>ナンド</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作について</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WASDで上下左右に移動します</t>
+    <rPh sb="5" eb="9">
+      <t>ジョウゲサユウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本を開く　ロッカーを開けるなどはSPACEキーで操作します</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新内容</t>
+    <rPh sb="0" eb="4">
+      <t>コウシンナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この仕様書はこのゲームのシナリオについての仕様書です</t>
+    <rPh sb="2" eb="5">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シナリオについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．夜の学校に忍び込んだ主人公</t>
+    <rPh sb="2" eb="3">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シノ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>シュジンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの答案を探しに職員室に侵入するも職員室に答案はなかった</t>
+    <rPh sb="4" eb="6">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ショクインシツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シンニュウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ショクインシツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校内のどこかにあるのではと思い校内を探索し始める</t>
+    <rPh sb="0" eb="2">
+      <t>コウナイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウナイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．見回りの先生に見つからないように、教室　理科室や音楽室様々な場所を探し答案を４つ集めることに成功する</t>
+    <rPh sb="2" eb="4">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="29" eb="34">
+      <t>サマザマナバショ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主人公は屋上から脱出することを目標とする</t>
+    <rPh sb="0" eb="3">
+      <t>シュジンコウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ダッシュツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．屋上に向かう途中、校長が現れ、校長につかまらないように屋上に向かう</t>
+    <rPh sb="2" eb="4">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．屋上のカギを開けるために最後の特殊問題に挑戦する</t>
+    <rPh sb="2" eb="4">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題に正解した主人公は屋上へ到達</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイカイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シュジンコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ムービーが流れ屋上から脱出に成功する</t>
+    <rPh sb="5" eb="6">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダッシュツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この仕様書はイベントについての仕様書です</t>
+    <rPh sb="2" eb="5">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームイベントについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このゲームでは様々な場所でイベントが発生します</t>
+    <rPh sb="7" eb="12">
+      <t>サマザマナバショ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．本を開くとき</t>
+    <rPh sb="2" eb="3">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いろいろな場所に本棚を設置しているので本棚のところにSPACEで開けるということを伝えたいです</t>
+    <rPh sb="5" eb="7">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本の内容は主に問題のヒントになります</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．何か物に注目するとき</t>
+    <rPh sb="2" eb="3">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チュウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何か注目するようなものにつけます</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室にある校長の銅像で主に使用します</t>
+    <rPh sb="0" eb="2">
+      <t>ビジュツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ドウゾウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．階段横に置くマップ</t>
+    <rPh sb="2" eb="5">
+      <t>カイダンヨコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップがどうなっているのかわかるように設置します</t>
+    <rPh sb="19" eb="21">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPACEキーを押すとマップが開くようにしたいです</t>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．ロッカーや机の中</t>
+    <rPh sb="7" eb="8">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案の発生場所について</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ハッセイバショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案はランダムに教室に２つ</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロッカーや机の中を探す時も！を表示して探せることをわかりやすくしたいです</t>
+    <rPh sb="5" eb="6">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図書室を除く理科室など名前の付いた部屋にランダム２つで出現させます</t>
+    <rPh sb="0" eb="3">
+      <t>トショシツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヘヤ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（図書室には全部ではなくとも４択のヒントを置きたいです）</t>
+    <rPh sb="1" eb="4">
+      <t>トショシツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>＊答案獲得のための４択問題は挑戦するかしないかの選択をさせ、押した瞬間始まって間違えてゲームオーバーとならないようにしたいです</t>
+    <rPh sb="1" eb="3">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>チョウセン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>シュンカンハジ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>マチガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案について</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>盗む答案は　国語　算数　理科　社会　の４種類あります</t>
+    <rPh sb="0" eb="1">
+      <t>ヌス</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コクゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>リカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シャカイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれ教科に基づいた問題を出します</t>
+    <rPh sb="4" eb="6">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国語なら国語　算数なら算数の問題を出します</t>
+    <rPh sb="0" eb="2">
+      <t>コクゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コクゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４択問題について</t>
+    <rPh sb="1" eb="2">
+      <t>タク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国語　</t>
+    <rPh sb="0" eb="2">
+      <t>コクゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>算数　</t>
+    <rPh sb="0" eb="2">
+      <t>サンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３＊４ー２＝？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.　６</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.　１０</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.  １４</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.  ５</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科</t>
+    <rPh sb="0" eb="2">
+      <t>リカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火が燃えるのに必要な物質は？</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブッシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．二酸化炭素</t>
+    <rPh sb="2" eb="7">
+      <t>ニサンカタンソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．水素</t>
+    <rPh sb="2" eb="4">
+      <t>スイソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．酸素</t>
+    <rPh sb="2" eb="4">
+      <t>サンソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．炭素</t>
+    <rPh sb="2" eb="4">
+      <t>タンソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社会</t>
+    <rPh sb="0" eb="2">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>邪馬台国を治めた人物は？</t>
+    <rPh sb="0" eb="4">
+      <t>ヤマタイコク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オサ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジンブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．聖徳太子</t>
+    <rPh sb="2" eb="6">
+      <t>ショウトクタイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．紫式部</t>
+    <rPh sb="2" eb="5">
+      <t>ムラサキシキブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．両面宿儺</t>
+    <rPh sb="2" eb="4">
+      <t>リョウメン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>スクナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．卑弥呼</t>
+    <rPh sb="2" eb="5">
+      <t>ヒミコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この問題を配置します</t>
+    <rPh sb="2" eb="4">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダムではなく固定沸きにしてバグが起こらないようにする</t>
+    <rPh sb="8" eb="10">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案の置き場所について</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国語：音楽室の指揮台のところに配置</t>
+    <rPh sb="0" eb="2">
+      <t>コクゴ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>算数：一階左から３つ目一番奥の部屋のロッカー</t>
+    <rPh sb="0" eb="2">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イッカイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>イチバンオク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特別問題について</t>
+    <rPh sb="0" eb="4">
+      <t>トクベツモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屋上から脱出するための問題についてです</t>
+    <rPh sb="0" eb="2">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダッシュツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長室の中にある校長の好物が答えになります</t>
+    <rPh sb="0" eb="3">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屋上特別問題</t>
+    <rPh sb="0" eb="2">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>トクベツモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長先生の好物は？</t>
+    <rPh sb="0" eb="4">
+      <t>コウチョウセンセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．ユッケ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．鮭おにぎり</t>
+    <rPh sb="2" eb="3">
+      <t>シャケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科：理科室の人体模型</t>
+    <rPh sb="0" eb="2">
+      <t>リカ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジンタイモケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判定はプレイヤーの体の外側と先生の正面足元に当たった時とする</t>
+    <rPh sb="0" eb="2">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カラダ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソトガワ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウメン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>アシモト</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（青鬼と同じ感じ）</t>
+    <rPh sb="1" eb="3">
+      <t>アオオニ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案以外のイベントについて</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教室の！が発生している場所</t>
+    <rPh sb="0" eb="2">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：机を開けた場合</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「机を探した　しかしなにもなかった」</t>
+    <rPh sb="1" eb="2">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロッカーを開けた場合</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ロッカーを探した　しかしなにもなかった」</t>
+    <rPh sb="6" eb="7">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（答案のない教室にも机１つ、ロッカー一つに！を付けて探せるようにしたいです）</t>
+    <rPh sb="1" eb="3">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科室の教卓に置いてある教科書</t>
+    <rPh sb="0" eb="3">
+      <t>リカシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョウタク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>キョウカショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「火が燃えるには酸素が必要不可欠！覚えておこう！」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サンソ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>ヒツヨウフカケツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室の校長の彫像</t>
+    <rPh sb="0" eb="3">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チョウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「校長先生の彫像らしい…　筋肉ムキムキだ」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>コウチョウセンセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チョウゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キンニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベントシートの答案の場所に記載</t>
+    <rPh sb="8" eb="10">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案の場所の変更</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室の本棚</t>
+    <rPh sb="0" eb="3">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「イラストの本しかないようだ…」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽室の楽譜棚</t>
+    <rPh sb="0" eb="3">
+      <t>オンガクシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガクフ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　楽譜が並んでいる…　全く読めない」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガクフ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マッタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽室のピアノ</t>
+    <rPh sb="0" eb="3">
+      <t>オンガクシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「立派なグランドピアノだ」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リッパ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長室の好物（校長の机の上にある）</t>
+    <rPh sb="0" eb="3">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屋上に入るとき</t>
+    <rPh sb="0" eb="2">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「屋上はカギがかけられている…」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オクジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題に挑戦しますか？</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答案の場所で問題に答えるとき</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「？にはカギがかけられている…」　</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（最初の？にはロッカーや引き出しが入る）</t>
+    <rPh sb="1" eb="3">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長の出現条件について</t>
+    <rPh sb="0" eb="2">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>シュツゲンジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長は４つの回答を集め、屋上に向かうフェーズに入った時に登場する</t>
+    <rPh sb="0" eb="2">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社会：2階校長室隣の教室の教卓</t>
+    <rPh sb="0" eb="2">
+      <t>シャカイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トナリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キョウタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追いかけてくる場所は屋上の問題を解く場所までとする</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>オクジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このシートはゲームフローをフローチャートで表したものです</t>
+    <rPh sb="21" eb="22">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フローチャート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フローチャート設定</t>
+    <rPh sb="7" eb="9">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特殊問題について</t>
+    <rPh sb="0" eb="4">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特殊問題（職員室で獲得するカギ）は間違えても見回りの先生に捕まらない（ゲームオーバーにならない）とする</t>
+    <rPh sb="0" eb="4">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ショクインシツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（特殊問題はこっちの自我で作ってるので、プレイヤーを巻き込みたくない）</t>
+    <rPh sb="1" eb="5">
+      <t>トクシュモンダイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジガ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>校長はプレイヤーよりもほんの少し遅くします</t>
+    <rPh sb="0" eb="2">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（捕まらない想定で作ってもらって大丈夫です</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ダイジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制作に余裕があったら校長に捕まった場合も作りたいです）</t>
+    <rPh sb="0" eb="2">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨユウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このシートでは答案怪盗JOKERのコンセプトを書いています</t>
+    <rPh sb="7" eb="9">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>コンセプト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -196,6 +2305,520 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>1マス６４＊６４に変更（粗くなりすぎたため）</t>
+    <rPh sb="9" eb="11">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーは96＊64とする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベントが発生する（本や隠し場所）では！を表示する（ドアを開けるときも）</t>
+    <rPh sb="5" eb="7">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>カクシバショ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（プレイヤーに分かりやすいようにしたいので、キャラクターの上に！を表示して何かできることをわかりやすくしたいです）</t>
+    <rPh sb="7" eb="8">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽室</t>
+    <rPh sb="0" eb="3">
+      <t>オンガクシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左上（ピアノ）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左下（楽器たち）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリシタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央上（指揮台）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央下（机といす）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツクエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右上ロッカー</t>
+    <rPh sb="0" eb="2">
+      <t>ミギウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右下（本棚）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術室</t>
+    <rPh sb="0" eb="3">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左（水道）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央（校長の彫像、校長登場の伏線用）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウチョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウゾウ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>コウチョウトウジョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フクセン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>彫像を囲うもの（イーゼルといす）</t>
+    <rPh sb="0" eb="2">
+      <t>チョウゾウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右上（美術の本棚）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギウエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ビジュツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右下（デッサンの本棚）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科室</t>
+    <rPh sb="0" eb="3">
+      <t>リカシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左下（ロッカー）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリシタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央（机といす）</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツクエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右上（本棚、ヒントがあります）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギウエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右中央（水道と教卓）</t>
+    <rPh sb="0" eb="3">
+      <t>ミギチュウオウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>スイドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右下（実験物を流す専用の水道）</t>
+    <rPh sb="0" eb="2">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ジッケンブツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>☆</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左上（人体模型）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ジンタイモケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナポリタンが好物</t>
+    <rPh sb="6" eb="8">
+      <t>コウブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．ナポリタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．ちくわ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左側の石（図書カウンター）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本棚（ヒントを置く）</t>
+    <rPh sb="0" eb="2">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：　「ナポリタンが…？　あまりいい気分ではない」</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間なしに変更、間違えたら捕まるようにします</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カウンター上の本棚（社会のヒント）</t>
+    <rPh sb="5" eb="6">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右から2列目上の本棚（国語のヒント）</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コクゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１F廊下</t>
+    <rPh sb="2" eb="4">
+      <t>ロウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一番左の茶色のドア（職員室）</t>
+    <rPh sb="0" eb="3">
+      <t>イチバンヒダリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ショクインシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白い手前のドアたち（教室）</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テマエ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白い奥のドア（理科室）</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>リカシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥の茶色のドア（図書室）</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>トショシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>階段横（地図）</t>
+    <rPh sb="0" eb="3">
+      <t>カイダンヨコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２F廊下</t>
+    <rPh sb="2" eb="4">
+      <t>ロウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左の茶色ドア（校長室）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>コウチョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下の白いドア（教室）</t>
+    <rPh sb="0" eb="1">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥の白いドア（音楽室）</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>オンガクシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右のちょっと茶色ドア（美術室）</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チャイロ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ビジュツシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左右端の台（地図）</t>
+    <rPh sb="0" eb="3">
+      <t>サユウハシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>（難しいテストを行わせない、実際の義賊のような感じ、小学生からは人気みたいな）</t>
     <rPh sb="1" eb="2">
       <t>ムズカ</t>
@@ -221,6 +2844,16 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>答案怪盗ASTER（アスター）</t>
+    <rPh sb="0" eb="2">
+      <t>トウアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>アンサーと盗む（スティール）、スクールの組みあわせ</t>
     <rPh sb="5" eb="6">
       <t>ヌス</t>
@@ -231,2802 +2864,284 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>音楽室</t>
-    <rPh sb="0" eb="3">
-      <t>オンガクシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左上（ピアノ）</t>
-    <rPh sb="0" eb="2">
-      <t>ヒダリウエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>☆</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左下（楽器たち）</t>
-    <rPh sb="0" eb="2">
-      <t>ヒダリシタ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガッキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>中央上（指揮台）</t>
-    <rPh sb="0" eb="2">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ウエ</t>
-    </rPh>
+    <t>ヒントの内容、場所について</t>
     <rPh sb="4" eb="6">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>中央下（机といす）</t>
-    <rPh sb="0" eb="2">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ツクエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右上ロッカー</t>
-    <rPh sb="0" eb="2">
-      <t>ミギウエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右下（本棚）</t>
-    <rPh sb="0" eb="2">
-      <t>ミギシタ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ホンダナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>美術室</t>
-    <rPh sb="0" eb="3">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左（水道）</t>
-    <rPh sb="0" eb="1">
-      <t>ヒダリ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>スイドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>中央（校長の彫像、校長登場の伏線用）</t>
-    <rPh sb="0" eb="2">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>チョウゾウ</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>コウチョウトウジョウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>フクセン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>彫像を囲うもの（イーゼルといす）</t>
-    <rPh sb="0" eb="2">
-      <t>チョウゾウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>カコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右上（美術の本棚）</t>
-    <rPh sb="0" eb="2">
-      <t>ミギウエ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ビジュツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ホンダナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右下（デッサンの本棚）</t>
-    <rPh sb="0" eb="2">
-      <t>ミギシタ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ホンダナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>理科室</t>
-    <rPh sb="0" eb="3">
-      <t>リカシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左上（人体模型）</t>
-    <rPh sb="0" eb="1">
-      <t>ヒダリ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>ジンタイモケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左下（ロッカー）</t>
-    <rPh sb="0" eb="2">
-      <t>ヒダリシタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>中央（机といす）</t>
-    <rPh sb="0" eb="2">
-      <t>チュウオウ</t>
-    </rPh>
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「この机にはカギがかかっている　問題に挑戦しますか？」</t>
     <rPh sb="3" eb="4">
       <t>ツクエ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右上（本棚、ヒントがあります）</t>
+    <rPh sb="16" eb="18">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ロッカーにはカギがかかっている　問題に挑戦しますか？」</t>
+    <rPh sb="17" eb="19">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国語のヒント　図書室の本棚</t>
     <rPh sb="0" eb="2">
-      <t>ミギウエ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+      <t>コクゴ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>トショシツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
       <t>ホンダナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>右中央（水道と教卓）</t>
-    <rPh sb="0" eb="3">
-      <t>ミギチュウオウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>スイドウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
+    <t>算数のヒント　１F左から2番目の教室の教卓</t>
+    <rPh sb="0" eb="2">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バンメ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
       <t>キョウタク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>右下（実験物を流す専用の水道）</t>
+    <t>「掛け算と割り算は足し算引き算よりも先に計算しよう！」</t>
+    <rPh sb="1" eb="2">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ザン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ザン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ザンヒ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ザン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「芥川龍之介　代表作：羅生門・鼻」</t>
+    <rPh sb="1" eb="6">
+      <t>アクタガワリュウノスケ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ダイヒョウサク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ラショウモン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科のヒント　理科室の本棚</t>
     <rPh sb="0" eb="2">
-      <t>ミギシタ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>ジッケンブツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センヨウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>スイドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左側の石（図書カウンター）</t>
-    <rPh sb="0" eb="2">
-      <t>ヒダリガワ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>イシ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>トショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>本棚（ヒントを置く）</t>
-    <rPh sb="0" eb="2">
-      <t>ホンダナ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カウンター上の本棚（社会のヒント）</t>
-    <rPh sb="5" eb="6">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ホンダナ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シャカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右から2列目上の本棚（国語のヒント）</t>
-    <rPh sb="0" eb="1">
-      <t>ミギ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>レツ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ホンダナ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コクゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１F廊下</t>
-    <rPh sb="2" eb="4">
-      <t>ロウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>一番左の茶色のドア（職員室）</t>
-    <rPh sb="0" eb="3">
-      <t>イチバンヒダリ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>チャイロ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ショクインシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>白い手前のドアたち（教室）</t>
-    <rPh sb="0" eb="1">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テマエ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>キョウシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>白い奥のドア（理科室）</t>
-    <rPh sb="0" eb="1">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>オク</t>
+      <t>リカ</t>
     </rPh>
     <rPh sb="7" eb="10">
       <t>リカシツ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奥の茶色のドア（図書室）</t>
-    <rPh sb="0" eb="1">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>チャイロ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>トショシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>階段横（地図）</t>
-    <rPh sb="0" eb="3">
-      <t>カイダンヨコ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>チズ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２F廊下</t>
-    <rPh sb="2" eb="4">
-      <t>ロウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左の茶色ドア（校長室）</t>
-    <rPh sb="0" eb="1">
-      <t>ヒダリ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>チャイロ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>下の白いドア（教室）</t>
-    <rPh sb="0" eb="1">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>キョウシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奥の白いドア（音楽室）</t>
-    <rPh sb="0" eb="1">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>オンガクシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>右のちょっと茶色ドア（美術室）</t>
-    <rPh sb="0" eb="1">
-      <t>ミギ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>チャイロ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左右端の台（地図）</t>
-    <rPh sb="0" eb="3">
-      <t>サユウハシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>チズ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長室</t>
-  </si>
-  <si>
-    <t>真ん中（机といす、来客用）</t>
-  </si>
-  <si>
-    <t>下（校長の机、パソコンと電話とナポリタンを置く）</t>
-  </si>
-  <si>
-    <t>机に注目したとき</t>
-  </si>
-  <si>
-    <t>シナリオに記載</t>
-  </si>
-  <si>
-    <t>一般教室</t>
-  </si>
-  <si>
-    <t>すべて教室はこのつくりでOK</t>
-  </si>
-  <si>
-    <t>左　教卓</t>
-  </si>
-  <si>
-    <t>一番右　ロッカー</t>
-  </si>
-  <si>
-    <t>廊下はスクロール式にする</t>
-  </si>
-  <si>
-    <t>更新日</t>
-    <rPh sb="0" eb="3">
-      <t>コウシンビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>変更者</t>
-    <rPh sb="0" eb="3">
-      <t>ヘンコウシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案回答JOKER仕様</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カイトウ</t>
+    <rPh sb="11" eb="13">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「火が燃えるには酸素が必要不可欠！覚えておこう！」</t>
+    <rPh sb="1" eb="2">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サンソ</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>ヒツヨウフカケツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「邪馬台国を治めた倭国の女王「卑弥呼」」</t>
+    <rPh sb="1" eb="5">
+      <t>ヤマタイコク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オサ</t>
     </rPh>
     <rPh sb="9" eb="11">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このページでは答案回答JOKERの仕様について書いています</t>
-    <rPh sb="7" eb="11">
-      <t>トウアンカイトウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>目的</t>
-    <rPh sb="0" eb="2">
-      <t>モクテキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>若きクリエーター展に向けた５分程度のカジュアル謎解きゲームを作る</t>
-    <rPh sb="0" eb="1">
-      <t>ワカ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>フンテイド</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ナゾト</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>夜の学校からテストの答えを盗む現実では味わえない体験をしてもらう</t>
-    <rPh sb="0" eb="1">
-      <t>ヨル</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ガッコウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヌス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ゲンジツ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>タイケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>詳細仕様</t>
-    <rPh sb="0" eb="4">
-      <t>ショウサイシヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案回答JOKERは夜の学校に侵入して答案を盗むゲームです</t>
-    <rPh sb="0" eb="4">
-      <t>トウアンカイトウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ヨル</t>
+      <t>ワコク</t>
     </rPh>
     <rPh sb="12" eb="14">
-      <t>ガッコウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シンニュウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ヌス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校内には見回りの先生が徘徊しているので見つからないようにします</t>
-    <rPh sb="0" eb="2">
-      <t>コウナイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ミマワ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ハイカイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校内に答案があるので見つけて学校から脱出すればクリアとなります</t>
-    <rPh sb="0" eb="2">
-      <t>コウナイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ガッコウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案は国語　算数　理科　社会　の４つあります</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コクゴ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>サンスウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>リカ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シャカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>問題は四択で出します</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨンタク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>それぞれ答案がある場所で教科に沿った問題に答えてもらいます</t>
-    <rPh sb="4" eb="6">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ソ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：国語</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コクゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この中で芥川龍之介が描いた本は？</t>
-    <rPh sb="2" eb="3">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="4" eb="9">
-      <t>アクタガワリュウノスケ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．人間失格</t>
-    <rPh sb="2" eb="6">
-      <t>ニンゲンシッカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．こころ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．羅生門</t>
-    <rPh sb="2" eb="5">
-      <t>ラショウモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．雨にも負けず</t>
-    <rPh sb="2" eb="3">
-      <t>アメ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答え：３．羅生門</t>
-    <rPh sb="0" eb="1">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ラショウモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>問題は２０秒以内に回答しないと見回りの先生に捕まってしまいます</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ビョウイナイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ミマワ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>制限時間なしに変更、間違えたら捕まるようにします</t>
-    <rPh sb="0" eb="4">
-      <t>セイゲンジカン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップ内にヒントを置くので活用して問題に挑んでもらいたいです</t>
-    <rPh sb="3" eb="4">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カツヨウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>イド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップについて</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップは廊下　教室　図書室　理科室　音楽室　美術室　校長室　（屋上）があります</t>
-    <rPh sb="4" eb="6">
-      <t>ロウカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>トショシツ</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>オクジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップの表示について</t>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップは若干斜めから見えているように表示します</t>
-    <rPh sb="4" eb="6">
-      <t>ジャッカン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ナナ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（イラストむずかったり、プログラムがむずくなったら見下ろしに変えます）</t>
-    <rPh sb="25" eb="27">
-      <t>ミオ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップとプレイヤーの大きさ、当たり判定について</t>
-    <rPh sb="10" eb="11">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このゲームは１マス３２＊３２となっています</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1マス６４＊６４に変更（粗くなりすぎたため）</t>
-    <rPh sb="9" eb="11">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーは４８＊３２で表示します</t>
-    <rPh sb="12" eb="14">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーは64＊64とする（１マスのところをとおれるようにするため）</t>
-  </si>
-  <si>
-    <t>廊下の大きさ　５＊５６</t>
-    <rPh sb="0" eb="2">
-      <t>ロウカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>教室　校長室の大きさ　１２＊１２</t>
-    <rPh sb="0" eb="2">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>シツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>図書室　　１５＊２５　理科室、美術室、音楽室　縦１５　横２０</t>
-  </si>
-  <si>
-    <t>マップのイメージはマインクラフトサーバーを参照すること</t>
-    <rPh sb="21" eb="23">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>当たり判定</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーと先生がぶつかったとき、プレイヤーは先生に捕まる</t>
-    <rPh sb="6" eb="8">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>判定はプレイヤーの体の外側と先生の正面足元に当たった時とする</t>
-    <rPh sb="0" eb="2">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カラダ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ソトガワ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ショウメン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>アシモト</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>トキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（青鬼と同じ感じ）</t>
-    <rPh sb="1" eb="3">
-      <t>アオオニ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップのイベントについて</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案の場所の変更</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案は音楽室と理科室に固定で出現させ、残りは教室にランダムで生成します</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コテイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イベントシートの答案の場所に記載</t>
-    <rPh sb="8" eb="10">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>図書室には４択問題のヒントが置かれています</t>
-    <rPh sb="0" eb="3">
-      <t>トショシツ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>タク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>階段横にマップ地図を設置してプレイヤーが迷子にならないようにします</t>
-    <rPh sb="0" eb="2">
-      <t>カイダン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヨコ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>チズ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>セッチ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>マイゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イベントが発生する（本や隠し場所）では！を表示する（ドアを開けるときも）</t>
-    <rPh sb="5" eb="7">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>カクシバショ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イベントはSPACEを押すことで始められる</t>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ハジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（プレイヤーに分かりやすいようにしたいので、キャラクターの上に！を表示して何かできることをわかりやすくしたいです）</t>
-    <rPh sb="7" eb="8">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ナニ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒント本を開いたときは文字を表示します</t>
-    <rPh sb="3" eb="4">
-      <t>ボン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：芥川龍之介　代表作：羅生門</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>アクタガワ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>リュウノスケ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ダイヒョウサク</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ラショウモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒントは何度も開けるようにしたいです</t>
-    <rPh sb="4" eb="6">
-      <t>ナンド</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>操作について</t>
-    <rPh sb="0" eb="2">
-      <t>ソウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>WASDで上下左右に移動します</t>
-    <rPh sb="5" eb="9">
-      <t>ジョウゲサユウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>本を開く　ロッカーを開けるなどはSPACEキーで操作します</t>
-    <rPh sb="0" eb="1">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ソウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SEやBGM、素材について</t>
-  </si>
-  <si>
-    <t>BGMは作る予定です（できなかったらフリー素材のやつを使います）</t>
-  </si>
-  <si>
-    <t>SEはフリー音源を使えるサイトがあるのでそこから使ってください</t>
-  </si>
-  <si>
-    <t>サイトURL</t>
-  </si>
-  <si>
-    <t>https://soundeffect-lab.info/</t>
-  </si>
-  <si>
-    <t>色々な素材（イラストなど）は下にサイトを載せるので使ってください</t>
-  </si>
-  <si>
-    <t>https://dot-illust.net/</t>
-  </si>
-  <si>
-    <t>←このサイトは３０種類まで無料で使えます</t>
-  </si>
-  <si>
-    <t>これ以外にもフリー素材は使って大丈夫ですが</t>
-  </si>
-  <si>
-    <t>利用規約は守ってください</t>
-  </si>
-  <si>
-    <t>マップと当たり判定をとりあえず作ってください</t>
-  </si>
-  <si>
-    <t>その際プレイヤーは葵ちゃんで代用してください</t>
-  </si>
-  <si>
-    <t>更新内容</t>
-    <rPh sb="0" eb="4">
-      <t>コウシンナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この仕様書はこのゲームのシナリオについての仕様書です</t>
-    <rPh sb="2" eb="5">
-      <t>シヨウショ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>シヨウショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シナリオについて</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．夜の学校に忍び込んだ主人公</t>
-    <rPh sb="2" eb="3">
-      <t>ヨル</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガッコウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>シノ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>シュジンコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テストの答案を探しに職員室に侵入するも職員室に答案はなかった</t>
-    <rPh sb="4" eb="6">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>サガ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ショクインシツ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シンニュウ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>ショクインシツ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>トウアン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校内のどこかにあるのではと思い校内を探索し始める</t>
-    <rPh sb="0" eb="2">
-      <t>コウナイ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウナイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>タンサク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ハジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．見回りの先生に見つからないように、教室　理科室や音楽室様々な場所を探し答案を４つ集めることに成功する</t>
-    <rPh sb="2" eb="4">
-      <t>ミマワ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="29" eb="34">
-      <t>サマザマナバショ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>サガ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>セイコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>主人公は屋上から脱出することを目標とする</t>
-    <rPh sb="0" eb="3">
-      <t>シュジンコウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ダッシュツ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>モクヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．屋上に向かう途中、校長が現れ、校長につかまらないように屋上に向かう</t>
-    <rPh sb="2" eb="4">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トチュウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>アラワ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ム</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．屋上のカギを開けるために最後の特殊問題に挑戦する</t>
-    <rPh sb="2" eb="4">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>チョウセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>問題に正解した主人公は屋上へ到達</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セイカイ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>シュジンコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>トウタツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ムービーが流れ屋上から脱出に成功する</t>
-    <rPh sb="5" eb="6">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ダッシュツ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セイコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案以外のイベントについて</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イガイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>教室の！が発生している場所</t>
-    <rPh sb="0" eb="2">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（答案のない教室にも机１つ、ロッカー一つに！を付けて探せるようにしたいです）</t>
-    <rPh sb="1" eb="3">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：机を開けた場合</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「机を探した　しかしなにもなかった」</t>
-    <rPh sb="1" eb="2">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロッカーを開けた場合</t>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「ロッカーを探した　しかしなにもなかった」</t>
-    <rPh sb="6" eb="7">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>理科室の教卓に置いてある教科書</t>
-    <rPh sb="0" eb="3">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キョウタク</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>キョウカショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「火が燃えるには酸素が必要不可欠！覚えておこう！」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>サンソ</t>
-    </rPh>
-    <rPh sb="14" eb="19">
-      <t>ヒツヨウフカケツ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>美術室の校長の彫像</t>
-    <rPh sb="0" eb="3">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>チョウゾウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「校長先生の彫像らしい…　筋肉ムキムキだ」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>コウチョウセンセイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チョウゾウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>キンニク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>美術室の本棚</t>
-    <rPh sb="0" eb="3">
-      <t>ビジュツシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホンダナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「イラストの本しかないようだ…」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音楽室の楽譜棚</t>
-    <rPh sb="0" eb="3">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガクフ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>タナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　楽譜が並んでいる…　全く読めない」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガクフ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ナラ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>マッタ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音楽室のピアノ</t>
-    <rPh sb="0" eb="3">
-      <t>オンガクシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「立派なグランドピアノだ」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>リッパ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長室の好物（校長の机の上にある）</t>
-    <rPh sb="0" eb="3">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウブツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ウエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「ナポリタンが…？　あまりいい気分ではない」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>キブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>屋上に入るとき</t>
-    <rPh sb="0" eb="2">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「屋上はカギがかけられている…」</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>オクジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>問題に挑戦しますか？</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>チョウセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案の場所で問題に答えるとき</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：　「？にはカギがかけられている…」　</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（最初の？にはロッカーや引き出しが入る）</t>
-    <rPh sb="1" eb="3">
-      <t>サイショ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長の出現条件について</t>
-    <rPh sb="0" eb="2">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>シュツゲンジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長は４つの回答を集め、屋上に向かうフェーズに入った時に登場する</t>
-    <rPh sb="0" eb="2">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>トウジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>追いかけてくる場所は屋上の問題を解く場所までとする</t>
-    <rPh sb="0" eb="1">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この仕様書はイベントについての仕様書です</t>
-    <rPh sb="2" eb="5">
-      <t>シヨウショ</t>
+      <t>ジョオウ</t>
     </rPh>
     <rPh sb="15" eb="18">
-      <t>シヨウショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームイベントについて</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このゲームでは様々な場所でイベントが発生します</t>
-    <rPh sb="7" eb="12">
-      <t>サマザマナバショ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ハッセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．本を開くとき</t>
-    <rPh sb="2" eb="3">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>いろいろな場所に本棚を設置しているので本棚のところにSPACEで開けるということを伝えたいです</t>
-    <rPh sb="5" eb="7">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ホンダナ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>セッチ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ホンダナ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ツタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>本の内容は主に問題のヒントになります</t>
-    <rPh sb="0" eb="1">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>モンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．何か物に注目するとき</t>
-    <rPh sb="2" eb="3">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>チュウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>何か注目するようなものにつけます</t>
-    <rPh sb="0" eb="1">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>チュウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>美術室にある校長の銅像で主に使用します</t>
-    <rPh sb="0" eb="2">
-      <t>ビジュツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ドウゾウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．階段横に置くマップ</t>
-    <rPh sb="2" eb="5">
-      <t>カイダンヨコ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップがどうなっているのかわかるように設置します</t>
-    <rPh sb="19" eb="21">
-      <t>セッチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SPACEキーを押すとマップが開くようにしたいです</t>
-    <rPh sb="8" eb="9">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．ロッカーや机の中</t>
-    <rPh sb="7" eb="8">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ナカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロッカーや机の中を探す時も！を表示して探せることをわかりやすくしたいです</t>
-    <rPh sb="5" eb="6">
-      <t>ツクエ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>サガ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案の発生場所について</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>ハッセイバショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案はランダムに教室に２つ</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>キョウシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>図書室を除く理科室など名前の付いた部屋にランダム２つで出現させます</t>
-    <rPh sb="0" eb="3">
-      <t>トショシツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ヘヤ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シュツゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ランダムではなく固定沸きにしてバグが起こらないようにする</t>
-    <rPh sb="8" eb="10">
-      <t>コテイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（図書室には全部ではなくとも４択のヒントを置きたいです）</t>
-    <rPh sb="1" eb="4">
-      <t>トショシツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゼンブ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>タク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>＊答案獲得のための４択問題は挑戦するかしないかの選択をさせ、押した瞬間始まって間違えてゲームオーバーとならないようにしたいです</t>
-    <rPh sb="1" eb="3">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>タク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>チョウセン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>シュンカンハジ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>マチガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案について</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>盗む答案は　国語　算数　理科　社会　の４種類あります</t>
-    <rPh sb="0" eb="1">
-      <t>ヌス</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コクゴ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サンスウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>リカ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シャカイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>それぞれ教科に基づいた問題を出します</t>
-    <rPh sb="4" eb="6">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>国語なら国語　算数なら算数の問題を出します</t>
-    <rPh sb="0" eb="2">
-      <t>コクゴ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コクゴ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>サンスウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>サンスウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４択問題について</t>
-    <rPh sb="1" eb="2">
-      <t>タク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>モンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特別問題について</t>
-    <rPh sb="0" eb="4">
-      <t>トクベツモンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>国語　</t>
-    <rPh sb="0" eb="2">
-      <t>コクゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>屋上から脱出するための問題についてです</t>
-    <rPh sb="0" eb="2">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ダッシュツ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>モンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長室の中にある校長の好物が答えになります</t>
-    <rPh sb="0" eb="3">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウブツ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ナポリタンが好物</t>
-    <rPh sb="6" eb="8">
-      <t>コウブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>屋上特別問題</t>
-    <rPh sb="0" eb="2">
-      <t>オクジョウ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>トクベツモンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長先生の好物は？</t>
-    <rPh sb="0" eb="4">
-      <t>コウチョウセンセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．ちくわ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．ユッケ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>算数　</t>
-    <rPh sb="0" eb="2">
-      <t>サンスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３＊４ー２＝？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．ナポリタン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1.　６</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．鮭おにぎり</t>
-    <rPh sb="2" eb="3">
-      <t>シャケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.　１０</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.  １４</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4.  ５</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>理科</t>
-    <rPh sb="0" eb="2">
-      <t>リカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>火が燃えるのに必要な物質は？</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ブッシツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．二酸化炭素</t>
-    <rPh sb="2" eb="7">
-      <t>ニサンカタンソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．水素</t>
-    <rPh sb="2" eb="4">
-      <t>スイソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．酸素</t>
-    <rPh sb="2" eb="4">
-      <t>サンソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．炭素</t>
-    <rPh sb="2" eb="4">
-      <t>タンソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>社会</t>
+      <t>ヒミコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社会のヒント　図書室カウンター上の本棚</t>
     <rPh sb="0" eb="2">
       <t>シャカイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>邪馬台国を治めた人物は？</t>
-    <rPh sb="0" eb="4">
-      <t>ヤマタイコク</t>
+    <rPh sb="7" eb="10">
+      <t>トショシツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホンダナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストボックスについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本このゲームでプレイヤーは言葉を発しません</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハッ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ロッカーにカギがかかっている」のように見たものを伝えたり、思ったことを伝えるくらいにします</t>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こんな感じでイメージしてます</t>
+    <rPh sb="3" eb="4">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見回りの先生の仕様</t>
+    <rPh sb="0" eb="2">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見回りの先生は各部屋に入ったときに６分の１の確率で出現します</t>
+    <rPh sb="0" eb="2">
+      <t>ミマワ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘヤ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先生は１５秒間追跡して、カウントが０になったときに部屋移動をすると追跡が終了する</t>
+    <rPh sb="0" eb="2">
+      <t>センセイ</t>
     </rPh>
     <rPh sb="5" eb="6">
-      <t>オサ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジンブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１．聖徳太子</t>
-    <rPh sb="2" eb="6">
-      <t>ショウトクタイシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２．紫式部</t>
-    <rPh sb="2" eb="5">
-      <t>ムラサキシキブ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３．両面宿儺</t>
-    <rPh sb="2" eb="4">
-      <t>リョウメン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>スクナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４．卑弥呼</t>
-    <rPh sb="2" eb="5">
-      <t>ヒミコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この問題を配置します</t>
-    <rPh sb="2" eb="4">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハイチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>答案の置き場所について</t>
-    <rPh sb="0" eb="2">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>国語：音楽室の指揮台のところに配置</t>
-    <rPh sb="0" eb="2">
-      <t>コクゴ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>オンガクシツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ハイチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>算数：一階左から３つ目一番奥の部屋のロッカー</t>
-    <rPh sb="0" eb="2">
-      <t>サンスウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヒダリ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>イチバンオク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヘヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>理科：理科室の人体模型</t>
-    <rPh sb="0" eb="2">
-      <t>リカ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>リカシツ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>ジンタイモケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>社会：2階校長室隣の教室の教卓</t>
-    <rPh sb="0" eb="2">
-      <t>シャカイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>コウチョウシツ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>トナリ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>キョウタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特殊問題について</t>
-    <rPh sb="0" eb="4">
-      <t>トクシュモンダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特殊問題（職員室で獲得するカギ）は間違えても見回りの先生に捕まらない（ゲームオーバーにならない）とする</t>
-    <rPh sb="0" eb="4">
-      <t>トクシュモンダイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ショクインシツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ミマワ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（特殊問題はこっちの自我で作ってるので、プレイヤーを巻き込みたくない）</t>
-    <rPh sb="1" eb="5">
-      <t>トクシュモンダイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジガ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このシートはゲームフローをフローチャートで表したものです</t>
-    <rPh sb="21" eb="22">
-      <t>アラワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フローチャート設定</t>
-    <rPh sb="7" eb="9">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フローチャート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>校長はプレイヤーよりもほんの少し遅くします</t>
-    <rPh sb="0" eb="2">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>オソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（捕まらない想定で作ってもらって大丈夫です</t>
-    <rPh sb="1" eb="2">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ソウテイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>ダイジョウブ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>制作に余裕があったら校長に捕まった場合も作りたいです）</t>
-    <rPh sb="0" eb="2">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨユウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウチョウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>教室は全体を映して大丈夫です</t>
-    <rPh sb="3" eb="5">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ウツ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>ダイジョウブ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦5マス　横５６マス</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦５　横５６</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦　１２　横１２</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦１２　横１２</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦１５　横２５</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦１５　横２０</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>縦　１５　横２０</t>
-    <rPh sb="0" eb="1">
-      <t>タテ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヨコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（当たり判定などは青鬼のようにしたいですが、壁と重なったり、ゲーム上なんかおかしいなどあったら</t>
-    <rPh sb="1" eb="2">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>アオオニ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>カサ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プログラマーの方でいい感じにしてくれると助かります）</t>
-    <rPh sb="7" eb="8">
-      <t>ホウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>タス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このシートでは答案怪盗JOKER（仮）のコンセプトを書いています</t>
-    <rPh sb="7" eb="9">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【答案怪盗アスター】に変更します</t>
-    <rPh sb="1" eb="3">
-      <t>トウアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヘンコウ</t>
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>カンツイセキ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>ヘヤイドウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ツイセキ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シュウリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3134,7 +3249,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3518,100 +3633,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEE246AD-433B-10C8-1F37-7296F975B44E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2DD8D51E-6166-462C-8F36-1C0602458345}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="676275" y="26727150"/>
-          <a:ext cx="5400675" cy="5133975"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>148</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5366430-7CA6-FD8F-490F-B62482B3CA14}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BEE246AD-433B-10C8-1F37-7296F975B44E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="714375" y="32632650"/>
-          <a:ext cx="5457825" cy="5238750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3659,6 +3680,106 @@
         <a:xfrm>
           <a:off x="2364105" y="5500687"/>
           <a:ext cx="3404235" cy="2532464"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>16668</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>49529</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="グラフィックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F81843-3161-47E6-8AE5-CBB4EF6290C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2164080" y="14494668"/>
+          <a:ext cx="4122420" cy="2318861"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>1428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>66042</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="グラフィックス 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E96D09E-AF5C-45D2-9276-97CE8EFD0467}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId5"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6987540" y="14479428"/>
+          <a:ext cx="4142742" cy="2330292"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7668,81 +7789,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C78DD1D-452A-4AC7-BC27-DE6E75E1AF27}">
   <dimension ref="K1:K19"/>
-  <sheetFormatPr defaultColWidth="2.25" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K4" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K14" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K18" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K19" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -7754,309 +7875,558 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FC5186-FD62-4BC4-B6C2-9C2D8535B64D}">
-  <dimension ref="B3:Q177"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <dimension ref="J3:Q114"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="10:12" x14ac:dyDescent="0.7">
+    <row r="3" spans="10:12" x14ac:dyDescent="0.45">
       <c r="J3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J9" t="s">
+        <v>180</v>
+      </c>
+      <c r="L9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="11:15" x14ac:dyDescent="0.45">
+      <c r="K25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="11:15" x14ac:dyDescent="0.45">
+      <c r="K26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="11:15" x14ac:dyDescent="0.45">
+      <c r="K27" t="s">
+        <v>183</v>
+      </c>
+      <c r="O27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="11:15" x14ac:dyDescent="0.45">
+      <c r="K28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="11:15" x14ac:dyDescent="0.45">
+      <c r="K29" t="s">
+        <v>185</v>
+      </c>
+      <c r="O29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="11:15" x14ac:dyDescent="0.45">
+      <c r="K30" t="s">
+        <v>186</v>
+      </c>
+      <c r="O30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L49" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>194</v>
+      </c>
+      <c r="N50" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>190</v>
+      </c>
+      <c r="O53" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="12:16" x14ac:dyDescent="0.45">
+      <c r="L71" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" spans="12:16" x14ac:dyDescent="0.45">
+      <c r="L72" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="73" spans="12:16" x14ac:dyDescent="0.45">
+      <c r="L73" t="s">
+        <v>202</v>
+      </c>
+      <c r="P73" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="12:16" x14ac:dyDescent="0.45">
+      <c r="L74" t="s">
+        <v>203</v>
+      </c>
+      <c r="P74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="92" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N92" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="93" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N93" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="94" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N94" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="95" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N95" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="96" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N96" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="97" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N97" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="109" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="Q109" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="Q110" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="111" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="Q111" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="112" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="Q112" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="113" spans="17:17" x14ac:dyDescent="0.45">
+      <c r="Q113" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="114" spans="17:17" x14ac:dyDescent="0.45">
+      <c r="Q114" t="s">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C43A3-048F-4D64-AC47-FC3BA283DCF5}">
+  <dimension ref="A1:Q120"/>
+  <sheetFormatPr defaultColWidth="5.59765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J4" t="s">
+    <row r="20" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F20" t="s">
         <v>14</v>
       </c>
-      <c r="L4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J5" t="s">
+    </row>
+    <row r="21" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J6" t="s">
+    <row r="22" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J7" t="s">
+    <row r="23" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J8" t="s">
+    <row r="24" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J9" t="s">
+    <row r="26" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E26" t="s">
         <v>20</v>
       </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="10:12" x14ac:dyDescent="0.7">
-      <c r="J10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="25" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K25" t="s">
+    </row>
+    <row r="28" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="5">
+        <v>45961</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K27" t="s">
+      <c r="P28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E29" t="s">
         <v>23</v>
       </c>
-      <c r="O27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K28" t="s">
+    </row>
+    <row r="31" spans="1:16" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K29" t="s">
+    <row r="32" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E32" t="s">
         <v>25</v>
       </c>
-      <c r="O29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K30" t="s">
+    </row>
+    <row r="34" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E34" t="s">
         <v>26</v>
       </c>
-      <c r="O30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="11:15" x14ac:dyDescent="0.7">
-      <c r="K31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="49" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L49" t="s">
+    </row>
+    <row r="35" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L50" t="s">
+    <row r="36" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E36" t="s">
         <v>28</v>
       </c>
-      <c r="N50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L51" t="s">
+    </row>
+    <row r="38" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L52" t="s">
+    <row r="55" spans="1:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E55" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="5">
+        <v>45958</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="53" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L53" t="s">
+      <c r="M56" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E57" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L54" t="s">
+      <c r="M57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E59" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L55" t="s">
+    <row r="60" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E61" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="12:15" x14ac:dyDescent="0.7">
-      <c r="L56" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="71" spans="12:16" x14ac:dyDescent="0.7">
-      <c r="L71" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72" spans="12:16" x14ac:dyDescent="0.7">
-      <c r="L72" t="s">
+    <row r="63" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E63" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="12:16" x14ac:dyDescent="0.7">
-      <c r="L73" t="s">
-        <v>36</v>
-      </c>
-      <c r="P73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="12:16" x14ac:dyDescent="0.7">
-      <c r="L74" t="s">
+    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E65" t="s">
         <v>37</v>
       </c>
-      <c r="P74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="12:16" x14ac:dyDescent="0.7">
-      <c r="L75" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="92" spans="14:14" x14ac:dyDescent="0.7">
-      <c r="N92" t="s">
+    </row>
+    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="14:14" x14ac:dyDescent="0.7">
-      <c r="N93" t="s">
+    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E68" t="s">
+        <v>118</v>
+      </c>
+      <c r="O68" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E70" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="14:14" x14ac:dyDescent="0.7">
-      <c r="N94" t="s">
+    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="5">
+        <v>45951</v>
+      </c>
+      <c r="B72" t="s">
+        <v>132</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="95" spans="14:14" x14ac:dyDescent="0.7">
-      <c r="N95" t="s">
+      <c r="Q72" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E74" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="14:14" x14ac:dyDescent="0.7">
-      <c r="N96" t="s">
+    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E75" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="14:17" x14ac:dyDescent="0.7">
-      <c r="N97" t="s">
+    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E77" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E78" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="14:17" x14ac:dyDescent="0.7">
-      <c r="N98" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="109" spans="14:17" x14ac:dyDescent="0.7">
-      <c r="Q109" t="s">
+    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E79" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E81" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="110" spans="14:17" x14ac:dyDescent="0.7">
-      <c r="Q110" t="s">
+    <row r="82" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E82" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="111" spans="14:17" x14ac:dyDescent="0.7">
-      <c r="Q111" t="s">
+    <row r="84" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E84" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="14:17" x14ac:dyDescent="0.7">
-      <c r="Q112" t="s">
+    <row r="86" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="4">
+        <v>45951</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="113" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="Q113" t="s">
+    <row r="88" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E88" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="Q114" t="s">
+    <row r="89" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E89" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="Q115" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="124" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="K124" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="125" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="K125" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="126" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="K126" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="127" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="K127" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="128" spans="11:17" x14ac:dyDescent="0.7">
-      <c r="K128" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="129" spans="11:11" x14ac:dyDescent="0.7">
-      <c r="K129" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="150" spans="11:11" x14ac:dyDescent="0.7">
-      <c r="K150" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="151" spans="11:11" x14ac:dyDescent="0.7">
-      <c r="K151" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="152" spans="11:11" x14ac:dyDescent="0.7">
-      <c r="K152" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="153" spans="11:11" x14ac:dyDescent="0.7">
-      <c r="K153" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="154" spans="11:11" x14ac:dyDescent="0.7">
-      <c r="K154" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B176" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B177" t="s">
-        <v>239</v>
+    <row r="91" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E91" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E93" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E94" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E97" s="7"/>
+    </row>
+    <row r="113" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E113" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="117" spans="5:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E117" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E119" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="120" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E120" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -8067,609 +8437,231 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C43A3-048F-4D64-AC47-FC3BA283DCF5}">
-  <dimension ref="A1:Q108"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C47E4FE-46DD-4F08-9A2A-B0D71841B40D}">
+  <dimension ref="A1:AK56"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E3" s="2" t="s">
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E10" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="F20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="G21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="G22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="G23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="G24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E26" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A28" s="5">
-        <v>45961</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E31" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E32" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E35" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E36" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="N38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E55" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A56" s="5">
-        <v>45958</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="M56" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E57" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="M57" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E59" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E60" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E61" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E65" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E67" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E68" t="s">
-        <v>101</v>
-      </c>
-      <c r="O68" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E70" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A72" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B72" t="s">
-        <v>104</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E74" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E75" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E78" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E79" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E81" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E82" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E84" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A86" s="4">
-        <v>45951</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E88" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E89" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E91" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E92" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E93" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E94" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E95" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="97" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E97" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="98" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E98" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="99" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E99" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="H99" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="101" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E101" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="102" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E102" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="105" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E105" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="106" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E106" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="107" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E107" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="108" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E108" t="s">
-        <v>248</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="E95" r:id="rId1" xr:uid="{8342DC88-1BA5-4642-9264-5231AFD2F0D1}"/>
-    <hyperlink ref="E99" r:id="rId2" xr:uid="{8D248A31-06D0-4209-A5A0-3C70DC7E6D84}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
-  <drawing r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C47E4FE-46DD-4F08-9A2A-B0D71841B40D}">
-  <dimension ref="A1:AI56"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
-  <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>45951</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="13:37" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M18" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M20" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O22" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P25" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M31" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M34" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O6" t="s">
+    <row r="35" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M35" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O7" t="s">
+    <row r="37" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M37" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M9" t="s">
+    <row r="38" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M38" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O10" t="s">
+    <row r="40" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M40" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M12" t="s">
+    <row r="41" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M41" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M14" t="s">
+    <row r="43" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M43" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O15" t="s">
+    <row r="44" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M44" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M46" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O16" t="s">
+    <row r="47" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M47" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="18" spans="13:35" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M18" s="3" t="s">
+    <row r="48" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P48" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M20" t="s">
+    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M50" t="s">
         <v>143</v>
       </c>
-      <c r="AI20" t="s">
+    </row>
+    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M51" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M21" t="s">
+      <c r="AE51" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O22" t="s">
+    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P52" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M54" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="P25" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M27" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="28" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M28" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M31" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="13:35" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M32" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M34" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M35" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M37" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="38" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M38" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="40" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M40" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="41" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M41" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="43" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M43" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="44" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M44" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M46" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="47" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M47" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="P48" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M50" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M51" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="P52" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M54" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="5">
         <v>45953</v>
       </c>
       <c r="M55" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M56" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -8680,343 +8672,388 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643C8F94-237C-4F52-86C7-FE7033AFCF0B}">
-  <dimension ref="A1:AR75"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <dimension ref="A1:AR89"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="2.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.3984375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="2.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>45951</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L12" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L17" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J22" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J23" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J24" s="6" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AO24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="27" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J27" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="29" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
         <v>45952</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J30" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="31" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J31" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J32" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="10:44" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="10:44" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J34" s="3" t="s">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="AK34" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J35" t="s">
+        <v>86</v>
+      </c>
+      <c r="N35" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O36" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O37" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK37" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="35" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J35" t="s">
+    <row r="38" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M41" t="s">
+        <v>20</v>
+      </c>
+      <c r="AR41" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AR42" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J43" t="s">
+        <v>87</v>
+      </c>
+      <c r="N43" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR43" t="s">
         <v>196</v>
       </c>
-      <c r="N35" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="36" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O36" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="37" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O37" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="38" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O38" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O39" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>200</v>
-      </c>
-      <c r="AR39" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="41" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="M41" t="s">
-        <v>80</v>
-      </c>
-      <c r="AR41" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="42" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="AR42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J43" t="s">
-        <v>204</v>
-      </c>
-      <c r="N43" t="s">
-        <v>205</v>
-      </c>
-      <c r="AR43" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="44" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    </row>
+    <row r="44" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O44" t="s">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="AR44" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="45" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O45" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O46" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O47" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="49" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J49" t="s">
-        <v>212</v>
+        <v>93</v>
       </c>
       <c r="N49" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O50" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O51" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="52" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="O53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="55" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J55" t="s">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="N55" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O57" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O58" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O59" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O60" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Y61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="10:25" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J63" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="71" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="10:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J73" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J74" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="75" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J75" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="10:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J78" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="57" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O57" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="58" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O58" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="59" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O59" t="s">
+    <row r="79" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K79" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="60" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="O60" t="s">
+    <row r="80" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K80" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="82" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K82" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="61" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="Y61" t="s">
+    <row r="83" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K83" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="10:25" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J63" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="65" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J65" t="s">
+    <row r="85" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K85" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J67" t="s">
+    <row r="86" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K86" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="69" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J69" t="s">
+    <row r="88" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K88" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K89" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J71" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="73" spans="10:10" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J73" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="74" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J74" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="75" spans="10:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="J75" t="s">
-        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -9029,45 +9066,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C73B12-1CE8-46A3-9E46-0FBD29283B60}">
   <dimension ref="A1:AA181"/>
-  <sheetFormatPr defaultColWidth="2.25" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K3" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>45952</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="Z179" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="Z180" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="AA181" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
+++ b/J/Document/答案回答JOKER仕様書(自動回復済み).xlsx
@@ -5,20 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\制作物\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\アスター\J\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C264F81E-5CAA-421A-A762-80CE16FE5F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE41C14-0355-4FC4-B99D-452BD7C18404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{036ADD24-4572-49F7-BC4A-1E84B3D7EC5D}"/>
   </bookViews>
   <sheets>
     <sheet name="コンセプト" sheetId="7" r:id="rId1"/>
     <sheet name="マップ" sheetId="8" r:id="rId2"/>
-    <sheet name="ゲームの仕様" sheetId="1" r:id="rId3"/>
-    <sheet name="シナリオ" sheetId="2" r:id="rId4"/>
-    <sheet name="イベント" sheetId="3" r:id="rId5"/>
-    <sheet name="フローチャート" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId3"/>
+    <sheet name="ゲームの仕様" sheetId="1" r:id="rId4"/>
+    <sheet name="シナリオ" sheetId="2" r:id="rId5"/>
+    <sheet name="イベント" sheetId="3" r:id="rId6"/>
+    <sheet name="フローチャート" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="257">
   <si>
     <t>更新日</t>
     <rPh sb="0" eb="3">
@@ -3142,6 +3143,215 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1階の床</t>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁下</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁上</t>
+    <rPh sb="0" eb="2">
+      <t>カベウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１F一つ目の教室に入るところ</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1F二つ目の教室に入るところ</t>
+    <rPh sb="2" eb="3">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>職員室入り口</t>
+    <rPh sb="0" eb="4">
+      <t>ショクインシツイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>グチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理科室入り口</t>
+    <rPh sb="0" eb="2">
+      <t>リカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>グチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図書室入り口</t>
+    <rPh sb="0" eb="4">
+      <t>トショシツイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>グチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>机（マップを置く予定）</t>
+    <rPh sb="0" eb="1">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左側の２Fへ行く階段</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右側の２Fへ行く階段</t>
+    <rPh sb="0" eb="2">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教室の床</t>
+    <rPh sb="0" eb="2">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>机</t>
+    <rPh sb="0" eb="1">
+      <t>ツクエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>椅子</t>
+    <rPh sb="0" eb="2">
+      <t>イス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロッカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左側の扉</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トビラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右側の扉</t>
+    <rPh sb="0" eb="2">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トビラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教卓</t>
+    <rPh sb="0" eb="2">
+      <t>キョウタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教室（１F左側の教室）</t>
+    <rPh sb="0" eb="2">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョウシツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3222,7 +3432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3245,6 +3455,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7789,79 +8002,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C78DD1D-452A-4AC7-BC27-DE6E75E1AF27}">
   <dimension ref="K1:K19"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.1875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K4" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K8" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K9" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="11:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K14" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K16" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K17" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="18" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K18" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K19" t="s">
         <v>218</v>
       </c>
@@ -7876,14 +8089,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FC5186-FD62-4BC4-B6C2-9C2D8535B64D}">
   <dimension ref="J3:Q114"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="3" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J3" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J4" t="s">
         <v>175</v>
       </c>
@@ -7891,27 +8104,27 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J7" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J8" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="10:12" x14ac:dyDescent="0.7">
       <c r="J9" t="s">
         <v>180</v>
       </c>
@@ -7919,17 +8132,17 @@
         <v>193</v>
       </c>
     </row>
-    <row r="25" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="11:15" x14ac:dyDescent="0.7">
       <c r="K25" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="11:15" x14ac:dyDescent="0.7">
       <c r="K26" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="27" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="27" spans="11:15" x14ac:dyDescent="0.7">
       <c r="K27" t="s">
         <v>183</v>
       </c>
@@ -7937,12 +8150,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="28" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="11:15" x14ac:dyDescent="0.7">
       <c r="K28" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="11:15" x14ac:dyDescent="0.7">
       <c r="K29" t="s">
         <v>185</v>
       </c>
@@ -7950,7 +8163,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="30" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="11:15" x14ac:dyDescent="0.7">
       <c r="K30" t="s">
         <v>186</v>
       </c>
@@ -7958,12 +8171,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="49" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="50" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L50" t="s">
         <v>194</v>
       </c>
@@ -7971,17 +8184,17 @@
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="51" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L51" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="52" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="52" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L52" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="53" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L53" t="s">
         <v>190</v>
       </c>
@@ -7989,27 +8202,27 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="54" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L54" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="12:15" x14ac:dyDescent="0.45">
+    <row r="55" spans="12:15" x14ac:dyDescent="0.7">
       <c r="L55" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="71" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="71" spans="12:16" x14ac:dyDescent="0.7">
       <c r="L71" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="72" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="72" spans="12:16" x14ac:dyDescent="0.7">
       <c r="L72" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="73" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="73" spans="12:16" x14ac:dyDescent="0.7">
       <c r="L73" t="s">
         <v>202</v>
       </c>
@@ -8017,7 +8230,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="74" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="74" spans="12:16" x14ac:dyDescent="0.7">
       <c r="L74" t="s">
         <v>203</v>
       </c>
@@ -8025,62 +8238,62 @@
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="92" spans="14:14" x14ac:dyDescent="0.7">
       <c r="N92" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="93" spans="14:14" x14ac:dyDescent="0.7">
       <c r="N93" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="94" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="94" spans="14:14" x14ac:dyDescent="0.7">
       <c r="N94" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="95" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="95" spans="14:14" x14ac:dyDescent="0.7">
       <c r="N95" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="96" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="96" spans="14:14" x14ac:dyDescent="0.7">
       <c r="N96" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="97" spans="14:17" x14ac:dyDescent="0.45">
+    <row r="97" spans="14:17" x14ac:dyDescent="0.7">
       <c r="N97" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="109" spans="14:17" x14ac:dyDescent="0.45">
+    <row r="109" spans="14:17" x14ac:dyDescent="0.7">
       <c r="Q109" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="110" spans="14:17" x14ac:dyDescent="0.45">
+    <row r="110" spans="14:17" x14ac:dyDescent="0.7">
       <c r="Q110" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="111" spans="14:17" x14ac:dyDescent="0.45">
+    <row r="111" spans="14:17" x14ac:dyDescent="0.7">
       <c r="Q111" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="112" spans="14:17" x14ac:dyDescent="0.45">
+    <row r="112" spans="14:17" x14ac:dyDescent="0.7">
       <c r="Q112" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="113" spans="17:17" x14ac:dyDescent="0.45">
+    <row r="113" spans="17:17" x14ac:dyDescent="0.7">
       <c r="Q113" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="114" spans="17:17" x14ac:dyDescent="0.45">
+    <row r="114" spans="17:17" x14ac:dyDescent="0.7">
       <c r="Q114" t="s">
         <v>215</v>
       </c>
@@ -8093,14 +8306,343 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65F72BF-4F77-43D6-9814-A6D923B3DD80}">
+  <dimension ref="K1:M72"/>
+  <sheetFormatPr defaultColWidth="2.0625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="10" width="2.0625" style="8"/>
+    <col min="11" max="11" width="7.5625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="2.0625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="11:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="11:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K4" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K5" s="8">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K7" s="8">
+        <v>20</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K8" s="8">
+        <v>30</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K10" s="8">
+        <v>103</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K11" s="8">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K12" s="8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K13" s="8">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K15" s="8">
+        <v>107</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K16" s="8">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K17" s="8">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K18" s="8">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K20" s="8">
+        <v>101</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K21" s="8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K23" s="8">
+        <v>113</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K24" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K25" s="8">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K26" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K27" s="8">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K28" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K29" s="8">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K30" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K32" s="8">
+        <v>117</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K33" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K34" s="8">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K35" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K36" s="8">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K37" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K38" s="8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K39" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K41" s="8">
+        <v>29</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K43" s="8">
+        <v>1001</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="44" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K44" s="8">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="46" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K46" s="8">
+        <v>1003</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K47" s="8">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K49" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K52" s="8">
+        <v>2</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K54" s="8">
+        <v>5</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K56" s="8">
+        <v>6</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K58" s="8">
+        <v>7</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K60" s="8">
+        <v>8</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K62" s="8">
+        <v>11</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="64" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K64" s="8">
+        <v>103.1</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K65" s="8">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="66" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K66" s="8">
+        <v>104.1</v>
+      </c>
+    </row>
+    <row r="67" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K67" s="8">
+        <v>104.2</v>
+      </c>
+    </row>
+    <row r="69" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K69" s="8">
+        <v>105.1</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="70" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K70" s="8">
+        <v>105.2</v>
+      </c>
+    </row>
+    <row r="71" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K71" s="8">
+        <v>106.1</v>
+      </c>
+    </row>
+    <row r="72" spans="11:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K72" s="8">
+        <v>106.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C43A3-048F-4D64-AC47-FC3BA283DCF5}">
   <dimension ref="A1:Q120"/>
-  <sheetFormatPr defaultColWidth="5.59765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.8125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8111,102 +8653,102 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A28" s="5">
         <v>45961</v>
       </c>
@@ -8217,47 +8759,47 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E32" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E34" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E36" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="5:14" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="N38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:13" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E55" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A56" s="5">
         <v>45958</v>
       </c>
@@ -8268,7 +8810,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E57" s="6" t="s">
         <v>31</v>
       </c>
@@ -8276,37 +8818,37 @@
         <v>171</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E59" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E60" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E61" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E63" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E65" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E68" t="s">
         <v>118</v>
       </c>
@@ -8314,12 +8856,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E70" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A72" s="5">
         <v>45951</v>
       </c>
@@ -8333,47 +8875,47 @@
         <v>131</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E74" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E75" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E77" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E78" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E79" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E81" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E82" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E84" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A86" s="4">
         <v>45951</v>
       </c>
@@ -8381,50 +8923,50 @@
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E88" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E89" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E91" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E93" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E94" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="97" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E97" s="7"/>
     </row>
-    <row r="113" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E113" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="117" spans="5:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="5:5" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E117" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="119" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E119" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="5:5" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E120" t="s">
         <v>236</v>
       </c>
@@ -8437,15 +8979,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C47E4FE-46DD-4F08-9A2A-B0D71841B40D}">
   <dimension ref="A1:AK56"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8456,12 +8998,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A4" s="4">
         <v>45951</v>
       </c>
@@ -8469,57 +9011,57 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="13:37" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="13:37" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M18" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M20" t="s">
         <v>121</v>
       </c>
@@ -8527,12 +9069,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O22" t="s">
         <v>123</v>
       </c>
@@ -8540,12 +9082,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="P25" t="s">
         <v>125</v>
       </c>
@@ -8553,87 +9095,87 @@
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M27" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M28" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M31" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="13:37" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M32" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M34" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M35" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M37" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M38" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M40" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M41" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M43" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M44" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M46" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M47" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="13:16" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="P48" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M50" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M51" t="s">
         <v>144</v>
       </c>
@@ -8641,17 +9183,17 @@
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="P52" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:31" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M54" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A55" s="5">
         <v>45953</v>
       </c>
@@ -8659,7 +9201,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M56" t="s">
         <v>149</v>
       </c>
@@ -8670,17 +9212,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643C8F94-237C-4F52-86C7-FE7033AFCF0B}">
   <dimension ref="A1:AR89"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.3984375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="2.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="2.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8688,12 +9230,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A4" s="4">
         <v>45951</v>
       </c>
@@ -8701,77 +9243,77 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L20" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J22" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J23" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J24" s="6" t="s">
         <v>78</v>
       </c>
@@ -8779,17 +9321,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J27" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:41" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="4">
         <v>45952</v>
       </c>
@@ -8797,22 +9339,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J30" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J31" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="10:44" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="10:44" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J34" s="3" t="s">
         <v>85</v>
       </c>
@@ -8820,7 +9362,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J35" t="s">
         <v>86</v>
       </c>
@@ -8831,7 +9373,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O36" t="s">
         <v>16</v>
       </c>
@@ -8839,7 +9381,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O37" t="s">
         <v>17</v>
       </c>
@@ -8847,12 +9389,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="38" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O38" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O39" t="s">
         <v>19</v>
       </c>
@@ -8863,7 +9405,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M41" t="s">
         <v>20</v>
       </c>
@@ -8871,12 +9413,12 @@
         <v>197</v>
       </c>
     </row>
-    <row r="42" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="AR42" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J43" t="s">
         <v>87</v>
       </c>
@@ -8887,7 +9429,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O44" t="s">
         <v>89</v>
       </c>
@@ -8895,22 +9437,22 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O45" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O46" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="10:44" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O47" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J49" t="s">
         <v>93</v>
       </c>
@@ -8918,27 +9460,27 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O51" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O52" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O53" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J55" t="s">
         <v>99</v>
       </c>
@@ -8946,112 +9488,112 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O57" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O58" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O59" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="O60" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="10:25" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="Y61" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="63" spans="10:25" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="10:25" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J63" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="65" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J65" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J67" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="69" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J69" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="71" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J71" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="73" spans="10:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="10:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J73" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="74" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J74" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="75" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J75" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="78" spans="10:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="10:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J78" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="79" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K79" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="80" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="10:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K80" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K82" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="83" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K83" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K85" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="86" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K86" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="88" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K88" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="11:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K89" t="s">
         <v>228</v>
       </c>
@@ -9063,15 +9605,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C73B12-1CE8-46A3-9E46-0FBD29283B60}">
   <dimension ref="A1:AA181"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.1875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9079,12 +9621,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K3" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A16" s="4">
         <v>45952</v>
       </c>
@@ -9092,17 +9634,17 @@
         <v>151</v>
       </c>
     </row>
-    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="Z179" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="Z180" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="26:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="AA181" t="s">
         <v>158</v>
       </c>
